--- a/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
   <si>
     <t>PAYO</t>
   </si>
@@ -656,86 +656,86 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -745,47 +745,50 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>224300</v>
+      </c>
+      <c r="E8" s="3">
         <v>208000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>206700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>192000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>183600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>158900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>148200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>137000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>139200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>122700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>110900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>100600</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -795,8 +798,8 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
@@ -804,8 +807,11 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -863,8 +869,11 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -922,8 +931,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,47 +957,48 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E12" s="3">
         <v>27000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>28000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>29300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>32900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>29600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>26600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>25900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>25500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>20100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>18500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>16700</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1004,8 +1017,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,49 +1079,52 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>600</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1122,47 +1141,50 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E15" s="3">
         <v>7100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5700</v>
-      </c>
-      <c r="G15" s="3">
-        <v>5300</v>
       </c>
       <c r="H15" s="3">
         <v>5300</v>
       </c>
       <c r="I15" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J15" s="3">
         <v>5200</v>
-      </c>
-      <c r="J15" s="3">
-        <v>4500</v>
       </c>
       <c r="K15" s="3">
         <v>4500</v>
       </c>
       <c r="L15" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="M15" s="3">
         <v>4400</v>
       </c>
       <c r="N15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="O15" s="3">
         <v>4600</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1172,8 +1194,8 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1181,8 +1203,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,55 +1226,56 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>198600</v>
+      </c>
+      <c r="E17" s="3">
         <v>178500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>173300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>177000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>192100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>164000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>150400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>143300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>143400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>129200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>129300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>101800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>100</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
+      <c r="R17" s="3">
+        <v>0</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
@@ -1260,47 +1286,50 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E18" s="3">
         <v>29500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>33400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-18400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1200</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1319,8 +1348,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,47 +1374,48 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>17900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-18700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>8000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>28500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-11500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>9200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1401,47 +1434,50 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E21" s="3">
         <v>30000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>57200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>23100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-17900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1460,8 +1496,11 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1519,55 +1558,58 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E23" s="3">
         <v>22800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>51300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>17100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-23800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>22200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
+      <c r="R23" s="3">
+        <v>0</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
@@ -1578,47 +1620,50 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E24" s="3">
         <v>10000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1700</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1628,8 +1673,8 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -1637,8 +1682,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,55 +1744,58 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E26" s="3">
         <v>12800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>45500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-26500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>20200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-18900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
+      <c r="R26" s="3">
+        <v>0</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
@@ -1755,55 +1806,58 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E27" s="3">
         <v>12800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>45500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-26500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>20200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-18900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
+      <c r="R27" s="3">
+        <v>0</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
@@ -1814,8 +1868,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1930,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +1992,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2054,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,47 +2116,50 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="E32" s="3">
         <v>6600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-17900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>18700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-8000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-28500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>11500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-9200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2109,55 +2178,58 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E33" s="3">
         <v>12800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>45500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-26500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>20200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-18900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
+      <c r="R33" s="3">
+        <v>0</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
@@ -2168,8 +2240,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,55 +2302,58 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E35" s="3">
         <v>12800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>45500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-26500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>20200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-18900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
+      <c r="R35" s="3">
+        <v>0</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
@@ -2286,61 +2364,64 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2350,8 +2431,11 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2457,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,55 +2481,56 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>617000</v>
+      </c>
+      <c r="E41" s="3">
         <v>590600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>581100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>544500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>543300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>507900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>492000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>465700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>465900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>449000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>498700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5600</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
+      <c r="R41" s="3">
+        <v>0</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
@@ -2455,8 +2541,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2514,44 +2603,47 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>66300</v>
+      </c>
+      <c r="E43" s="3">
         <v>65000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>59000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>61300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>61200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>62500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>60500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>63800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>67500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>59800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>61500</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2564,8 +2656,8 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -2573,8 +2665,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2632,43 +2727,46 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6425400</v>
+      </c>
+      <c r="E45" s="3">
         <v>5405700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5568900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5512900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5866600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5069700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5167400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4656000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4429300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3737700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3655800</v>
-      </c>
-      <c r="N45" s="3">
-        <v>400</v>
       </c>
       <c r="O45" s="3">
         <v>400</v>
@@ -2677,11 +2775,11 @@
         <v>400</v>
       </c>
       <c r="Q45" s="3">
+        <v>400</v>
+      </c>
+      <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,56 +2789,59 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7108700</v>
+      </c>
+      <c r="E46" s="3">
         <v>6061300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6208900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6118800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6471100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5640200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5719900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5185500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4962700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4246500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4215900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>100</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2750,8 +2851,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2765,28 +2869,28 @@
         <v>0</v>
       </c>
       <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
         <v>6400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6600</v>
-      </c>
-      <c r="J47" s="3">
-        <v>7000</v>
       </c>
       <c r="K47" s="3">
         <v>7000</v>
       </c>
       <c r="L47" s="3">
+        <v>7000</v>
+      </c>
+      <c r="M47" s="3">
         <v>6900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6800</v>
-      </c>
-      <c r="N47" s="3">
-        <v>754800</v>
       </c>
       <c r="O47" s="3">
         <v>754800</v>
@@ -2794,8 +2898,8 @@
       <c r="P47" s="3">
         <v>754800</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>754800</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -2809,44 +2913,47 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E48" s="3">
         <v>26100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>29600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>29700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>30800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>26000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27100</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2859,8 +2966,8 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -2868,44 +2975,47 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>96200</v>
+      </c>
+      <c r="E49" s="3">
         <v>90800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>77800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>70000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>65300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>58600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>59300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>60800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>58700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>56900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>57300</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2918,8 +3028,8 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -2927,8 +3037,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3099,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,44 +3161,47 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E52" s="3">
         <v>39600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>30800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>22100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>22400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>24000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>23600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>23900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>26400</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3095,8 +3214,8 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -3104,8 +3223,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,56 +3285,59 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7283100</v>
+      </c>
+      <c r="E54" s="3">
         <v>6217800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6343900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6237700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6594700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5759500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5842300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5307900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5078800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4360200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4333500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>759200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>760300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>760700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>100</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3222,8 +3347,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3373,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,52 +3397,53 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E57" s="3">
         <v>35600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>31800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41600</v>
-      </c>
-      <c r="H57" s="3">
-        <v>26700</v>
       </c>
       <c r="I57" s="3">
         <v>26700</v>
       </c>
       <c r="J57" s="3">
+        <v>26700</v>
+      </c>
+      <c r="K57" s="3">
         <v>17400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17200</v>
-      </c>
-      <c r="L57" s="3">
-        <v>16900</v>
       </c>
       <c r="M57" s="3">
         <v>16900</v>
       </c>
       <c r="N57" s="3">
+        <v>16900</v>
+      </c>
+      <c r="O57" s="3">
         <v>2100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
+      <c r="Q57" s="3">
+        <v>0</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
@@ -3327,8 +3457,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3368,14 +3501,14 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
@@ -3386,56 +3519,59 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6508000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5475200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5629300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5554300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5935900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5126600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5214100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4699000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4480600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3784100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3755400</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
         <v>100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3445,56 +3581,59 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6542000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5510800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5658400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5586100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5977500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5153400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5240900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4716300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4497800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3801000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3772300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>100</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3">
         <v>100</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,38 +3643,41 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E61" s="3">
         <v>15800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>15700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>14800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3563,53 +3705,56 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>58500</v>
+      </c>
+      <c r="E62" s="3">
         <v>53200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>43800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>57700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>55700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>57700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>43700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>55200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>80200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>67300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>79400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>85400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>79500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>30300</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3622,8 +3767,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3829,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +3891,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,56 +3953,59 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6618800</v>
+      </c>
+      <c r="E66" s="3">
         <v>5579800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5717900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5660900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6049400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5226800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5299400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4785900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4591700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3868300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3851700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>87500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>79600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>30300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>100</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3858,8 +4015,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4041,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4101,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4163,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4058,8 +4225,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,55 +4287,58 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-42200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-55000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-100600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-108500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-98400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-71900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-76300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-94100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-75200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-76000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-18200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-9200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-100</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
+      <c r="R72" s="3">
+        <v>0</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
@@ -4176,8 +4349,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4411,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4473,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,55 +4535,58 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>664300</v>
+      </c>
+      <c r="E76" s="3">
         <v>638000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>625900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>576800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>545300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>532600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>542900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>522000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>487100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>491900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>481800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>671600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>680700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>730400</v>
       </c>
-      <c r="Q76" s="3">
-        <v>0</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
+      <c r="R76" s="3">
+        <v>0</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
@@ -4412,8 +4597,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,61 +4659,64 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4535,55 +4726,58 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E81" s="3">
         <v>12800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>45500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-26500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>20200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-18900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
+      <c r="R81" s="3">
+        <v>0</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
@@ -4594,8 +4788,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,47 +4814,48 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E83" s="3">
         <v>7100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5200</v>
-      </c>
-      <c r="J83" s="3">
-        <v>4500</v>
       </c>
       <c r="K83" s="3">
         <v>4500</v>
       </c>
       <c r="L83" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="M83" s="3">
         <v>4400</v>
       </c>
       <c r="N83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="O83" s="3">
         <v>4700</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4667,8 +4865,8 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -4676,8 +4874,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +4936,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +4998,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5060,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5122,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,55 +5184,58 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E89" s="3">
         <v>41400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>56000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>39600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>26500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
@@ -5030,8 +5246,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,47 +5272,48 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5103,8 +5323,8 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -5112,8 +5332,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5394,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,49 +5456,52 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E94" s="3">
         <v>15700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-57000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>19700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>20600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-62500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>28000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>14700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>300</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -5280,8 +5509,8 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -5289,8 +5518,11 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +5544,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5371,8 +5604,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5666,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5728,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,55 +5790,58 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1004700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-177300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>49000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-364500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>805600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-96100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>518200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>233600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>709300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>34200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>650200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2400</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>760800</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
@@ -5607,47 +5852,50 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-900</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5657,8 +5905,8 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -5666,55 +5914,58 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1071500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-121500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>98800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-417100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>865500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-60900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>479800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>263900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>733400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>23000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>669800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5600</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
@@ -5723,6 +5974,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
   <si>
     <t>PAYO</t>
   </si>
@@ -656,89 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -748,50 +749,53 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>228200</v>
+      </c>
+      <c r="E8" s="3">
         <v>224300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>208000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>206700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>192000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>183600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>158900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>148200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>137000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>139200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>122700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>110900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>100600</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,8 +805,8 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
@@ -810,8 +814,11 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -872,8 +879,11 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -934,8 +944,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -958,50 +971,51 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E12" s="3">
         <v>35000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>27000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>28000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>29300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>32900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>29600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>25900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>25500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>20100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>18500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>16700</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1020,8 +1034,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1082,52 +1099,55 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1144,50 +1164,53 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E15" s="3">
         <v>8800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5700</v>
-      </c>
-      <c r="H15" s="3">
-        <v>5300</v>
       </c>
       <c r="I15" s="3">
         <v>5300</v>
       </c>
       <c r="J15" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K15" s="3">
         <v>5200</v>
-      </c>
-      <c r="K15" s="3">
-        <v>4500</v>
       </c>
       <c r="L15" s="3">
         <v>4500</v>
       </c>
       <c r="M15" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="N15" s="3">
         <v>4400</v>
       </c>
       <c r="O15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="P15" s="3">
         <v>4600</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1197,8 +1220,8 @@
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1206,8 +1229,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1227,58 +1253,59 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>189800</v>
+      </c>
+      <c r="E17" s="3">
         <v>198600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>178500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>173300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>177000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>192100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>164000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>150400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>143300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>143400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>129200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>129300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>101800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>100</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
+      <c r="S17" s="3">
+        <v>0</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
@@ -1289,50 +1316,53 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E18" s="3">
         <v>25700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>29500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>33400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-18400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1200</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1351,8 +1381,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1375,50 +1408,51 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E20" s="3">
         <v>15600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>17900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-18700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>28500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-11500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>9200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1437,50 +1471,53 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E21" s="3">
         <v>50000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>30000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>57200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>23100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-17900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>11000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>26600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-11200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-4900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1499,8 +1536,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1561,58 +1601,61 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E23" s="3">
         <v>41300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>51300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>17100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-23800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>22200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
+      <c r="S23" s="3">
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
@@ -1623,50 +1666,53 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E24" s="3">
         <v>14300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1700</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1676,8 +1722,8 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1685,8 +1731,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1747,58 +1796,61 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E26" s="3">
         <v>27000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>45500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-26500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>20200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-18900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
+      <c r="S26" s="3">
+        <v>0</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
@@ -1809,58 +1861,61 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E27" s="3">
         <v>27000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>45500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-26500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>20200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-18900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
+      <c r="S27" s="3">
+        <v>0</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
@@ -1871,8 +1926,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1933,8 +1991,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1995,8 +2056,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2057,8 +2121,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2119,50 +2186,53 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-15600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-17900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>18700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-28500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>11500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-9200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2181,58 +2251,61 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E33" s="3">
         <v>27000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>45500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-26500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>20200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-18900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
+      <c r="S33" s="3">
+        <v>0</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
@@ -2243,8 +2316,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2305,58 +2381,61 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E35" s="3">
         <v>27000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>45500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-26500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>20200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-18900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
+      <c r="S35" s="3">
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
@@ -2367,64 +2446,67 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2434,8 +2516,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2458,8 +2543,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2482,58 +2568,59 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>587200</v>
+      </c>
+      <c r="E41" s="3">
         <v>617000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>590600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>581100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>544500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>543300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>507900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>492000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>465700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>465900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>449000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>498700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5600</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
+      <c r="S41" s="3">
+        <v>0</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
@@ -2544,8 +2631,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2606,47 +2696,50 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E43" s="3">
         <v>66300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>65000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>59000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>61300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>61200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>62500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>60500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>63800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>67500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>59800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>61500</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2659,8 +2752,8 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -2668,8 +2761,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2730,46 +2826,49 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5961200</v>
+      </c>
+      <c r="E45" s="3">
         <v>6425400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5405700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5568900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5512900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5866600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5069700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5167400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4656000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4429300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3737700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3655800</v>
-      </c>
-      <c r="O45" s="3">
-        <v>400</v>
       </c>
       <c r="P45" s="3">
         <v>400</v>
@@ -2778,11 +2877,11 @@
         <v>400</v>
       </c>
       <c r="R45" s="3">
+        <v>400</v>
+      </c>
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,59 +2891,62 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6616100</v>
+      </c>
+      <c r="E46" s="3">
         <v>7108700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6061300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6208900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6118800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6471100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5640200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5719900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5185500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4962700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4246500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4215900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>100</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2854,13 +2956,16 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3">
         <v>0</v>
@@ -2872,28 +2977,28 @@
         <v>0</v>
       </c>
       <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
         <v>6400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6600</v>
-      </c>
-      <c r="K47" s="3">
-        <v>7000</v>
       </c>
       <c r="L47" s="3">
         <v>7000</v>
       </c>
       <c r="M47" s="3">
+        <v>7000</v>
+      </c>
+      <c r="N47" s="3">
         <v>6900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6800</v>
-      </c>
-      <c r="O47" s="3">
-        <v>754800</v>
       </c>
       <c r="P47" s="3">
         <v>754800</v>
@@ -2901,8 +3006,8 @@
       <c r="Q47" s="3">
         <v>754800</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>754800</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -2916,47 +3021,50 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E48" s="3">
         <v>40400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>29600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>29700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>32500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>30800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>26000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27100</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2969,8 +3077,8 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -2978,47 +3086,50 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>102500</v>
+      </c>
+      <c r="E49" s="3">
         <v>96200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>90800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>77800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>70000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>65300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>58600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>59300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>60800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>58700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>56900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>57300</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3031,8 +3142,8 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3040,8 +3151,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3102,8 +3216,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3164,47 +3281,50 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E52" s="3">
         <v>37900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>39600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>30800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>22100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>23600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>26400</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3217,8 +3337,8 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -3226,8 +3346,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3288,59 +3411,62 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6795500</v>
+      </c>
+      <c r="E54" s="3">
         <v>7283100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6217800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6343900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6237700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6594700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5759500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5842300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5307900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5078800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4360200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4333500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>759200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>760300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>760700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>100</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3476,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3374,8 +3503,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3398,55 +3528,56 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E57" s="3">
         <v>33900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>35600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>29200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>31800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>41600</v>
-      </c>
-      <c r="I57" s="3">
-        <v>26700</v>
       </c>
       <c r="J57" s="3">
         <v>26700</v>
       </c>
       <c r="K57" s="3">
+        <v>26700</v>
+      </c>
+      <c r="L57" s="3">
         <v>17400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17200</v>
-      </c>
-      <c r="M57" s="3">
-        <v>16900</v>
       </c>
       <c r="N57" s="3">
         <v>16900</v>
       </c>
       <c r="O57" s="3">
+        <v>16900</v>
+      </c>
+      <c r="P57" s="3">
         <v>2100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
+      <c r="R57" s="3">
+        <v>0</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
@@ -3460,8 +3591,11 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3504,14 +3638,14 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
@@ -3522,59 +3656,62 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6024900</v>
+      </c>
+      <c r="E59" s="3">
         <v>6508000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5475200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5629300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5554300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5935900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5126600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5214100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4699000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4480600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3784100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3755400</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3">
         <v>100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3584,59 +3721,62 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6060100</v>
+      </c>
+      <c r="E60" s="3">
         <v>6542000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5510800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5658400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5586100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5977500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5153400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5240900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4716300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4497800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3801000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3772300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>100</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3">
         <v>100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3646,41 +3786,44 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E61" s="3">
         <v>18400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>15700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>14800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3708,56 +3851,59 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>59400</v>
+      </c>
+      <c r="E62" s="3">
         <v>58500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>53200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>43800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>57700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>55700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>57700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>43700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>55200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>80200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>67300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>79400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>85400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>79500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>30300</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3770,8 +3916,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3832,8 +3981,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3894,8 +4046,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3956,59 +4111,62 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6133900</v>
+      </c>
+      <c r="E66" s="3">
         <v>6618800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5579800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5717900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5660900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6049400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5226800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5299400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4785900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4591700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3868300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3851700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>87500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>79600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>30300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>100</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4018,8 +4176,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4042,8 +4203,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4104,8 +4266,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4166,8 +4331,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4228,8 +4396,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4290,58 +4461,61 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-15200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-42200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-55000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-100600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-108500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-98400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-71900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-76300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-94100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-75200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-76000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-18200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-100</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
+      <c r="S72" s="3">
+        <v>0</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
@@ -4352,8 +4526,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4414,8 +4591,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4476,8 +4656,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4538,58 +4721,61 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>661500</v>
+      </c>
+      <c r="E76" s="3">
         <v>664300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>638000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>625900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>576800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>545300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>532600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>542900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>522000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>487100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>491900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>481800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>671600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>680700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>730400</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
+      <c r="S76" s="3">
+        <v>0</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
@@ -4600,8 +4786,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4662,64 +4851,67 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4729,58 +4921,61 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E81" s="3">
         <v>27000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>45500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-26500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>20200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-18900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
+      <c r="S81" s="3">
+        <v>0</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
@@ -4791,8 +4986,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4815,50 +5013,51 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E83" s="3">
         <v>8800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5200</v>
-      </c>
-      <c r="K83" s="3">
-        <v>4500</v>
       </c>
       <c r="L83" s="3">
         <v>4500</v>
       </c>
       <c r="M83" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="N83" s="3">
         <v>4400</v>
       </c>
       <c r="O83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="P83" s="3">
         <v>4700</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4868,8 +5067,8 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -4877,8 +5076,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4939,8 +5141,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5001,8 +5206,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5063,8 +5271,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5125,8 +5336,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5187,58 +5401,61 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E89" s="3">
         <v>58200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>41400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>56000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>39600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>15500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>26500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>17800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-400</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
@@ -5249,8 +5466,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5273,50 +5493,51 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5326,8 +5547,8 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -5335,8 +5556,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5397,8 +5621,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5459,52 +5686,55 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-114100</v>
+      </c>
+      <c r="E94" s="3">
         <v>3500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>15700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-57000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>19700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>20600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-62500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>28000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>14700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>300</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -5512,8 +5742,8 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -5521,8 +5751,11 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5545,8 +5778,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5607,8 +5841,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5669,8 +5906,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5731,8 +5971,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5793,58 +6036,61 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-521100</v>
+      </c>
+      <c r="E100" s="3">
         <v>1004700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-177300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>49000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-364500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>805600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-96100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>518200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>233600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>709300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>34200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>650200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2400</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>760800</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
@@ -5855,50 +6101,53 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E101" s="3">
         <v>5100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-900</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5908,8 +6157,8 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -5917,58 +6166,61 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-597300</v>
+      </c>
+      <c r="E102" s="3">
         <v>1071500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-121500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>98800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-417100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>865500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-60900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>479800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>263900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>733400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>23000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>669800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5600</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
@@ -5977,6 +6229,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>PAYO</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,53 +753,56 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>239500</v>
+      </c>
+      <c r="E8" s="3">
         <v>228200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>224300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>208000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>206700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>192000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>183600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>158900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>148200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>137000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>139200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>122700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>110900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>100600</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -808,8 +812,8 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
@@ -817,8 +821,11 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -882,8 +889,11 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,8 +957,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,53 +985,54 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E12" s="3">
         <v>32100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>35000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>28000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>29300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>32900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>29600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>26600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>25900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>25500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>20100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>18500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16700</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1051,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,55 +1119,58 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1167,53 +1187,56 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E15" s="3">
         <v>9400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5700</v>
-      </c>
-      <c r="I15" s="3">
-        <v>5300</v>
       </c>
       <c r="J15" s="3">
         <v>5300</v>
       </c>
       <c r="K15" s="3">
+        <v>5300</v>
+      </c>
+      <c r="L15" s="3">
         <v>5200</v>
-      </c>
-      <c r="L15" s="3">
-        <v>4500</v>
       </c>
       <c r="M15" s="3">
         <v>4500</v>
       </c>
       <c r="N15" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="O15" s="3">
         <v>4400</v>
       </c>
       <c r="P15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="Q15" s="3">
         <v>4600</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1223,8 +1246,8 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1232,8 +1255,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,61 +1280,62 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>193200</v>
+      </c>
+      <c r="E17" s="3">
         <v>189800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>198600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>178500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>173300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>177000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>192100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>164000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>150400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>143300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>143400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>129200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>129300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>101800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>100</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
+      <c r="T17" s="3">
+        <v>0</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
@@ -1319,53 +1346,56 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E18" s="3">
         <v>38400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>25700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>29500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>33400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>15000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-18400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1384,8 +1414,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,53 +1442,54 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>4500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>15600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>17900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-18700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>28500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-11500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-600</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1474,53 +1508,56 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E21" s="3">
         <v>52300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>50000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>30000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>57200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>23100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>11000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>26600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-11200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,8 +1576,11 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1604,61 +1644,64 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>48300</v>
+      </c>
+      <c r="E23" s="3">
         <v>42900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>41300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>51300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>17100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-23800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>22200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
+      <c r="T23" s="3">
+        <v>0</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
@@ -1669,53 +1712,56 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E24" s="3">
         <v>13900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1700</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1725,8 +1771,8 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1734,8 +1780,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,61 +1848,64 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E26" s="3">
         <v>29000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>27000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>45500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-26500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>20200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-12400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
+      <c r="T26" s="3">
+        <v>0</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
@@ -1864,61 +1916,64 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E27" s="3">
         <v>29000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>27000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>45500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>20200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
+      <c r="T27" s="3">
+        <v>0</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
@@ -1929,8 +1984,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,8 +2052,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2059,8 +2120,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,53 +2256,56 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-15600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-17900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>18700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-28500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>11500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>600</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2254,61 +2324,64 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E33" s="3">
         <v>29000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>27000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>45500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>20200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-18900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
+      <c r="T33" s="3">
+        <v>0</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
@@ -2319,8 +2392,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,61 +2460,64 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E35" s="3">
         <v>29000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>27000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>45500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>20200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-18900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
+      <c r="T35" s="3">
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
@@ -2449,67 +2528,70 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2519,8 +2601,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,61 +2655,62 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>575700</v>
+      </c>
+      <c r="E41" s="3">
         <v>587200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>617000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>590600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>581100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>544500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>543300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>507900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>492000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>465700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>465900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>449000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>498700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5600</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
+      <c r="T41" s="3">
+        <v>0</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
@@ -2634,8 +2721,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2699,50 +2789,53 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>68700</v>
+      </c>
+      <c r="E43" s="3">
         <v>67800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>66300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>65000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>59000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>61300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>61200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>62500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>60500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>63800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>67500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>59800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>61500</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2755,8 +2848,8 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -2764,8 +2857,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2829,49 +2925,52 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6088500</v>
+      </c>
+      <c r="E45" s="3">
         <v>5961200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6425400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5405700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5568900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5512900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5866600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5069700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5167400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4656000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4429300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3737700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3655800</v>
-      </c>
-      <c r="P45" s="3">
-        <v>400</v>
       </c>
       <c r="Q45" s="3">
         <v>400</v>
@@ -2880,11 +2979,11 @@
         <v>400</v>
       </c>
       <c r="S45" s="3">
+        <v>400</v>
+      </c>
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,62 +2993,65 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6732900</v>
+      </c>
+      <c r="E46" s="3">
         <v>6616100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7108700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6061300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6208900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6118800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6471100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5640200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5719900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5185500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4962700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4246500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4215900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>100</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2959,16 +3061,19 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F47" s="3">
         <v>0</v>
@@ -2980,28 +3085,28 @@
         <v>0</v>
       </c>
       <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
         <v>6400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6600</v>
-      </c>
-      <c r="L47" s="3">
-        <v>7000</v>
       </c>
       <c r="M47" s="3">
         <v>7000</v>
       </c>
       <c r="N47" s="3">
+        <v>7000</v>
+      </c>
+      <c r="O47" s="3">
         <v>6900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6800</v>
-      </c>
-      <c r="P47" s="3">
-        <v>754800</v>
       </c>
       <c r="Q47" s="3">
         <v>754800</v>
@@ -3009,8 +3114,8 @@
       <c r="R47" s="3">
         <v>754800</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>754800</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -3024,50 +3129,53 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E48" s="3">
         <v>37500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>40400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>29600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>32000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>32500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>30800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>27100</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3080,8 +3188,8 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3089,50 +3197,53 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>108500</v>
+      </c>
+      <c r="E49" s="3">
         <v>102500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>96200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>90800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>77800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>70000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>65300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>58600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>59300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>60800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>58700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>56900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>57300</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3145,8 +3256,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3154,8 +3265,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,50 +3401,53 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E52" s="3">
         <v>39300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>37900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>39600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>30800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>22400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>24000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>23600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>23900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>26400</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3340,8 +3460,8 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3349,8 +3469,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,62 +3537,65 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6920300</v>
+      </c>
+      <c r="E54" s="3">
         <v>6795500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7283100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6217800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6343900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6237700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6594700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5759500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5842300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5307900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5078800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4360200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4333500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>759200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>760300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>760700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>100</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3479,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,58 +3659,59 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E57" s="3">
         <v>35300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>33900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>35600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>31800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>41600</v>
-      </c>
-      <c r="J57" s="3">
-        <v>26700</v>
       </c>
       <c r="K57" s="3">
         <v>26700</v>
       </c>
       <c r="L57" s="3">
+        <v>26700</v>
+      </c>
+      <c r="M57" s="3">
         <v>17400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>16900</v>
       </c>
       <c r="O57" s="3">
         <v>16900</v>
       </c>
       <c r="P57" s="3">
+        <v>16900</v>
+      </c>
+      <c r="Q57" s="3">
         <v>2100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+      <c r="S57" s="3">
+        <v>0</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
@@ -3594,31 +3725,34 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>15000</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3641,14 +3775,14 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -3659,62 +3793,65 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6137500</v>
+      </c>
+      <c r="E59" s="3">
         <v>6024900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6508000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5475200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5629300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5554300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5935900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5126600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5214100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4699000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4480600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3784100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3755400</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3">
         <v>100</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3724,62 +3861,65 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6191500</v>
+      </c>
+      <c r="E60" s="3">
         <v>6060100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6542000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5510800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5658400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5586100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5977500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5153400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5240900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4716300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4497800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3801000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3772300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>100</v>
       </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
       <c r="S60" s="3">
+        <v>0</v>
+      </c>
+      <c r="T60" s="3">
         <v>100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3789,44 +3929,47 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>14400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>15700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13700</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3854,59 +3997,62 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E62" s="3">
         <v>59400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>58500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>53200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>43800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>57700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>55700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>57700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>43700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>55200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>80200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>67300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>79400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>85400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>79500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>30300</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3919,8 +4065,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,62 +4269,65 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6250900</v>
+      </c>
+      <c r="E66" s="3">
         <v>6133900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6618800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5579800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5717900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5660900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6049400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5226800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5299400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4785900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4591700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3868300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3851700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>87500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>79600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>30300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4179,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4399,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,61 +4635,64 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E72" s="3">
         <v>13800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-15200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-42200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-55000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-100600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-108500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-98400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-71900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-76300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-94100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-75200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-76000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-18200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-9200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-100</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
+      <c r="T72" s="3">
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
@@ -4529,8 +4703,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,61 +4907,64 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>669400</v>
+      </c>
+      <c r="E76" s="3">
         <v>661500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>664300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>638000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>625900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>576800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>545300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>532600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>542900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>522000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>487100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>491900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>481800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>671600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>680700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>730400</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
@@ -4789,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,67 +5043,70 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4924,61 +5116,64 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E81" s="3">
         <v>29000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>27000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>45500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>20200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-18900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
+      <c r="T81" s="3">
+        <v>0</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
@@ -4989,8 +5184,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,53 +5212,54 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E83" s="3">
         <v>9400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>4500</v>
       </c>
       <c r="M83" s="3">
         <v>4500</v>
       </c>
       <c r="N83" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="O83" s="3">
         <v>4400</v>
       </c>
       <c r="P83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="Q83" s="3">
         <v>4700</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5070,8 +5269,8 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -5079,8 +5278,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,61 +5618,64 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E89" s="3">
         <v>39500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>58200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>41400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>56000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>39600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>26500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>17800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
@@ -5469,8 +5686,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,53 +5714,54 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-15700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5550,8 +5771,8 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -5559,8 +5780,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,55 +5916,58 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-551200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-114100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>3500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>15700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-57000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>19700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>20600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-62500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>28000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>14700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>300</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5745,8 +5975,8 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -5754,8 +5984,11 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,8 +6012,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5844,8 +6078,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,61 +6282,64 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>77600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-521100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1004700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-177300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>49000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-364500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>805600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-96100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>518200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>233600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>709300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>34200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>650200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2400</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>760800</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
@@ -6104,53 +6350,56 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-900</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6160,8 +6409,8 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -6169,61 +6418,64 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-432900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-597300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1071500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-121500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>98800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-417100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>865500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-60900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>479800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>263900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>733400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>23000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>669800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5600</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
@@ -6232,6 +6484,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD970DE-299F-4320-B34B-138C177B4DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9345"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PAYO" sheetId="6" r:id="rId1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>PAYO</t>
   </si>
@@ -303,7 +304,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
@@ -369,9 +370,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -409,9 +410,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -446,7 +447,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -481,7 +482,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -654,9 +655,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -675,21 +676,20 @@
     <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
@@ -744,20 +744,8 @@
       <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -812,20 +800,8 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
-      <c r="X8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -880,20 +856,8 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -948,20 +912,8 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -982,12 +934,8 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1042,20 +990,8 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1110,20 +1046,8 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-      <c r="U13" s="3">
-        <v>0</v>
-      </c>
-      <c r="V13" s="3">
-        <v>0</v>
-      </c>
-      <c r="W13" s="3">
-        <v>0</v>
-      </c>
-      <c r="X13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1178,20 +1102,8 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1246,20 +1158,8 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
-      </c>
-      <c r="W15" s="3">
-        <v>0</v>
-      </c>
-      <c r="X15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1277,12 +1177,8 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1337,20 +1233,8 @@
       <c r="T17" s="3">
         <v>0</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1405,20 +1289,8 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1439,12 +1311,8 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1499,20 +1367,8 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1567,20 +1423,8 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1635,20 +1479,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1703,20 +1535,8 @@
       <c r="T23" s="3">
         <v>0</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1771,20 +1591,8 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1839,20 +1647,8 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-      <c r="U25" s="3">
-        <v>0</v>
-      </c>
-      <c r="V25" s="3">
-        <v>0</v>
-      </c>
-      <c r="W25" s="3">
-        <v>0</v>
-      </c>
-      <c r="X25" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1907,20 +1703,8 @@
       <c r="T26" s="3">
         <v>0</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1975,20 +1759,8 @@
       <c r="T27" s="3">
         <v>0</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2043,20 +1815,8 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-      <c r="U28" s="3">
-        <v>0</v>
-      </c>
-      <c r="V28" s="3">
-        <v>0</v>
-      </c>
-      <c r="W28" s="3">
-        <v>0</v>
-      </c>
-      <c r="X28" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2111,20 +1871,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2179,20 +1927,8 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-      <c r="U30" s="3">
-        <v>0</v>
-      </c>
-      <c r="V30" s="3">
-        <v>0</v>
-      </c>
-      <c r="W30" s="3">
-        <v>0</v>
-      </c>
-      <c r="X30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2247,20 +1983,8 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-      <c r="U31" s="3">
-        <v>0</v>
-      </c>
-      <c r="V31" s="3">
-        <v>0</v>
-      </c>
-      <c r="W31" s="3">
-        <v>0</v>
-      </c>
-      <c r="X31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2315,20 +2039,8 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2383,20 +2095,8 @@
       <c r="T33" s="3">
         <v>0</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2451,20 +2151,8 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-      <c r="U34" s="3">
-        <v>0</v>
-      </c>
-      <c r="V34" s="3">
-        <v>0</v>
-      </c>
-      <c r="W34" s="3">
-        <v>0</v>
-      </c>
-      <c r="X34" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2519,25 +2207,13 @@
       <c r="T35" s="3">
         <v>0</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
@@ -2592,20 +2268,8 @@
       <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2626,12 +2290,8 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2652,12 +2312,8 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2712,20 +2368,8 @@
       <c r="T41" s="3">
         <v>0</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2780,20 +2424,8 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2848,20 +2480,8 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
-      <c r="X43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2916,20 +2536,8 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
-      </c>
-      <c r="V44" s="3">
-        <v>0</v>
-      </c>
-      <c r="W44" s="3">
-        <v>0</v>
-      </c>
-      <c r="X44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2984,20 +2592,8 @@
       <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3052,20 +2648,8 @@
       <c r="T46" s="3">
         <v>100</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3120,20 +2704,8 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3188,20 +2760,8 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
-      <c r="X48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3256,20 +2816,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V49" s="3">
-        <v>0</v>
-      </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
-      <c r="X49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3324,20 +2872,8 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-      <c r="U50" s="3">
-        <v>0</v>
-      </c>
-      <c r="V50" s="3">
-        <v>0</v>
-      </c>
-      <c r="W50" s="3">
-        <v>0</v>
-      </c>
-      <c r="X50" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3392,20 +2928,8 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-      <c r="U51" s="3">
-        <v>0</v>
-      </c>
-      <c r="V51" s="3">
-        <v>0</v>
-      </c>
-      <c r="W51" s="3">
-        <v>0</v>
-      </c>
-      <c r="X51" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3460,20 +2984,8 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3528,20 +3040,8 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-      <c r="U53" s="3">
-        <v>0</v>
-      </c>
-      <c r="V53" s="3">
-        <v>0</v>
-      </c>
-      <c r="W53" s="3">
-        <v>0</v>
-      </c>
-      <c r="X53" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3596,20 +3096,8 @@
       <c r="T54" s="3">
         <v>100</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3630,12 +3118,8 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-      <c r="U55" s="3"/>
-      <c r="V55" s="3"/>
-      <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3656,12 +3140,8 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-      <c r="U56" s="3"/>
-      <c r="V56" s="3"/>
-      <c r="W56" s="3"/>
-      <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3716,20 +3196,8 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3784,20 +3252,8 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3852,20 +3308,8 @@
       <c r="T59" s="3">
         <v>100</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3920,20 +3364,8 @@
       <c r="T60" s="3">
         <v>100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3988,20 +3420,8 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4056,20 +3476,8 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4124,20 +3532,8 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-      <c r="U63" s="3">
-        <v>0</v>
-      </c>
-      <c r="V63" s="3">
-        <v>0</v>
-      </c>
-      <c r="W63" s="3">
-        <v>0</v>
-      </c>
-      <c r="X63" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4192,20 +3588,8 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-      <c r="U64" s="3">
-        <v>0</v>
-      </c>
-      <c r="V64" s="3">
-        <v>0</v>
-      </c>
-      <c r="W64" s="3">
-        <v>0</v>
-      </c>
-      <c r="X64" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4260,20 +3644,8 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-      <c r="U65" s="3">
-        <v>0</v>
-      </c>
-      <c r="V65" s="3">
-        <v>0</v>
-      </c>
-      <c r="W65" s="3">
-        <v>0</v>
-      </c>
-      <c r="X65" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4328,20 +3700,8 @@
       <c r="T66" s="3">
         <v>100</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4362,12 +3722,8 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-      <c r="U67" s="3"/>
-      <c r="V67" s="3"/>
-      <c r="W67" s="3"/>
-      <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4422,20 +3778,8 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-      <c r="U68" s="3">
-        <v>0</v>
-      </c>
-      <c r="V68" s="3">
-        <v>0</v>
-      </c>
-      <c r="W68" s="3">
-        <v>0</v>
-      </c>
-      <c r="X68" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4490,20 +3834,8 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-      <c r="U69" s="3">
-        <v>0</v>
-      </c>
-      <c r="V69" s="3">
-        <v>0</v>
-      </c>
-      <c r="W69" s="3">
-        <v>0</v>
-      </c>
-      <c r="X69" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4558,20 +3890,8 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4626,20 +3946,8 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-      <c r="U71" s="3">
-        <v>0</v>
-      </c>
-      <c r="V71" s="3">
-        <v>0</v>
-      </c>
-      <c r="W71" s="3">
-        <v>0</v>
-      </c>
-      <c r="X71" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4694,20 +4002,8 @@
       <c r="T72" s="3">
         <v>0</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4762,20 +4058,8 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-      <c r="U73" s="3">
-        <v>0</v>
-      </c>
-      <c r="V73" s="3">
-        <v>0</v>
-      </c>
-      <c r="W73" s="3">
-        <v>0</v>
-      </c>
-      <c r="X73" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4830,20 +4114,8 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-      <c r="U74" s="3">
-        <v>0</v>
-      </c>
-      <c r="V74" s="3">
-        <v>0</v>
-      </c>
-      <c r="W74" s="3">
-        <v>0</v>
-      </c>
-      <c r="X74" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4898,20 +4170,8 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-      <c r="U75" s="3">
-        <v>0</v>
-      </c>
-      <c r="V75" s="3">
-        <v>0</v>
-      </c>
-      <c r="W75" s="3">
-        <v>0</v>
-      </c>
-      <c r="X75" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -4966,20 +4226,8 @@
       <c r="T76" s="3">
         <v>0</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5034,25 +4282,13 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-      <c r="U77" s="3">
-        <v>0</v>
-      </c>
-      <c r="V77" s="3">
-        <v>0</v>
-      </c>
-      <c r="W77" s="3">
-        <v>0</v>
-      </c>
-      <c r="X77" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
@@ -5107,20 +4343,8 @@
       <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5175,20 +4399,8 @@
       <c r="T81" s="3">
         <v>0</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5209,12 +4421,8 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-      <c r="U82" s="3"/>
-      <c r="V82" s="3"/>
-      <c r="W82" s="3"/>
-      <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5269,20 +4477,8 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5337,20 +4533,8 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-      <c r="U84" s="3">
-        <v>0</v>
-      </c>
-      <c r="V84" s="3">
-        <v>0</v>
-      </c>
-      <c r="W84" s="3">
-        <v>0</v>
-      </c>
-      <c r="X84" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5405,20 +4589,8 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-      <c r="U85" s="3">
-        <v>0</v>
-      </c>
-      <c r="V85" s="3">
-        <v>0</v>
-      </c>
-      <c r="W85" s="3">
-        <v>0</v>
-      </c>
-      <c r="X85" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5473,20 +4645,8 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-      <c r="U86" s="3">
-        <v>0</v>
-      </c>
-      <c r="V86" s="3">
-        <v>0</v>
-      </c>
-      <c r="W86" s="3">
-        <v>0</v>
-      </c>
-      <c r="X86" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5541,20 +4701,8 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-      <c r="U87" s="3">
-        <v>0</v>
-      </c>
-      <c r="V87" s="3">
-        <v>0</v>
-      </c>
-      <c r="W87" s="3">
-        <v>0</v>
-      </c>
-      <c r="X87" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5609,20 +4757,8 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-      <c r="U88" s="3">
-        <v>0</v>
-      </c>
-      <c r="V88" s="3">
-        <v>0</v>
-      </c>
-      <c r="W88" s="3">
-        <v>0</v>
-      </c>
-      <c r="X88" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5677,20 +4813,8 @@
       <c r="T89" s="3">
         <v>0</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5711,12 +4835,8 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-      <c r="U90" s="3"/>
-      <c r="V90" s="3"/>
-      <c r="W90" s="3"/>
-      <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5771,20 +4891,8 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5839,20 +4947,8 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-      <c r="U92" s="3">
-        <v>0</v>
-      </c>
-      <c r="V92" s="3">
-        <v>0</v>
-      </c>
-      <c r="W92" s="3">
-        <v>0</v>
-      </c>
-      <c r="X92" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5907,20 +5003,8 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-      <c r="U93" s="3">
-        <v>0</v>
-      </c>
-      <c r="V93" s="3">
-        <v>0</v>
-      </c>
-      <c r="W93" s="3">
-        <v>0</v>
-      </c>
-      <c r="X93" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5975,20 +5059,8 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6009,12 +5081,8 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-      <c r="U95" s="3"/>
-      <c r="V95" s="3"/>
-      <c r="W95" s="3"/>
-      <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6069,20 +5137,8 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6137,20 +5193,8 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-      <c r="U97" s="3">
-        <v>0</v>
-      </c>
-      <c r="V97" s="3">
-        <v>0</v>
-      </c>
-      <c r="W97" s="3">
-        <v>0</v>
-      </c>
-      <c r="X97" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6205,20 +5249,8 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-      <c r="U98" s="3">
-        <v>0</v>
-      </c>
-      <c r="V98" s="3">
-        <v>0</v>
-      </c>
-      <c r="W98" s="3">
-        <v>0</v>
-      </c>
-      <c r="X98" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6273,20 +5305,8 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-      <c r="U99" s="3">
-        <v>0</v>
-      </c>
-      <c r="V99" s="3">
-        <v>0</v>
-      </c>
-      <c r="W99" s="3">
-        <v>0</v>
-      </c>
-      <c r="X99" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6341,20 +5361,8 @@
       <c r="T100" s="3">
         <v>0</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6409,20 +5417,8 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6476,18 +5472,6 @@
       </c>
       <c r="T102" s="3">
         <v>0</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD970DE-299F-4320-B34B-138C177B4DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="PAYO" sheetId="6" r:id="rId1"/>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
   <si>
     <t>PAYO</t>
   </si>
@@ -304,7 +303,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
@@ -370,9 +369,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -410,9 +409,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -447,7 +446,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -482,7 +481,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -655,176 +654,183 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>248300</v>
+      </c>
+      <c r="E8" s="3">
         <v>239500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>228200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>224300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>208000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>206700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>192000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>183600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>158900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>148200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>137000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>139200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>122700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>110900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>100600</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>34000</v>
+      </c>
+      <c r="G9" s="3">
+        <v>36300</v>
+      </c>
+      <c r="H9" s="3">
+        <v>30400</v>
+      </c>
+      <c r="I9" s="3">
+        <v>28500</v>
+      </c>
+      <c r="J9" s="3">
+        <v>27100</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -856,31 +862,34 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>210200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>202600</v>
+      </c>
+      <c r="F10" s="3">
+        <v>194200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>188000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>177600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>178200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>164900</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -912,8 +921,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,64 +946,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E12" s="3">
         <v>27600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>32100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>35000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>27000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>28000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>29300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>32900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>26600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>25900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>25500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>20100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>18500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>16700</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,120 +1062,129 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>300</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E15" s="3">
         <v>10700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>5300</v>
       </c>
       <c r="K15" s="3">
         <v>5300</v>
       </c>
       <c r="L15" s="3">
+        <v>5300</v>
+      </c>
+      <c r="M15" s="3">
         <v>5200</v>
-      </c>
-      <c r="M15" s="3">
-        <v>4500</v>
       </c>
       <c r="N15" s="3">
         <v>4500</v>
       </c>
       <c r="O15" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="P15" s="3">
         <v>4400</v>
       </c>
       <c r="Q15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="R15" s="3">
         <v>4600</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>208800</v>
+      </c>
+      <c r="E17" s="3">
         <v>193200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>189800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>198600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>178500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>173300</v>
       </c>
-      <c r="I17" s="3">
-        <v>177000</v>
-      </c>
       <c r="J17" s="3">
+        <v>176700</v>
+      </c>
+      <c r="K17" s="3">
         <v>192100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>164000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>150400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>143300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>143400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>129200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>129300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>101800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>100</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E18" s="3">
         <v>46300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>38400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>25700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>29500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>33400</v>
       </c>
-      <c r="I18" s="3">
-        <v>15000</v>
-      </c>
       <c r="J18" s="3">
+        <v>15300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-8500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1200</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,143 +1343,150 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>2000</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>4500</v>
+        <v>-2000</v>
       </c>
       <c r="F20" s="3">
-        <v>15600</v>
+        <v>-1800</v>
       </c>
       <c r="G20" s="3">
-        <v>-6600</v>
+        <v>-15600</v>
       </c>
       <c r="H20" s="3">
-        <v>17900</v>
+        <v>7800</v>
       </c>
       <c r="I20" s="3">
-        <v>2100</v>
+        <v>-17900</v>
       </c>
       <c r="J20" s="3">
+        <v>300</v>
+      </c>
+      <c r="K20" s="3">
         <v>6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-18700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>28500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-11500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>9200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-600</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>51600</v>
+      </c>
+      <c r="E21" s="3">
         <v>59000</v>
       </c>
-      <c r="E21" s="3">
-        <v>52300</v>
-      </c>
       <c r="F21" s="3">
+        <v>49500</v>
+      </c>
+      <c r="G21" s="3">
         <v>50000</v>
       </c>
-      <c r="G21" s="3">
-        <v>30000</v>
-      </c>
       <c r="H21" s="3">
+        <v>28800</v>
+      </c>
+      <c r="I21" s="3">
         <v>57200</v>
       </c>
-      <c r="I21" s="3">
-        <v>23100</v>
-      </c>
       <c r="J21" s="3">
+        <v>20800</v>
+      </c>
+      <c r="K21" s="3">
         <v>2800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>26600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-11200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1479,120 +1518,129 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E23" s="3">
         <v>48300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>42900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>41300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>22800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>51300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>17100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-23800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>22200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-15800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E24" s="3">
         <v>15900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>13900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>10000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1700</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E26" s="3">
         <v>32400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>29000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>27000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>45500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-26500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E27" s="3">
         <v>32400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>29000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>27000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>12800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>45500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>20200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1871,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-2000</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>-4500</v>
+        <v>2000</v>
       </c>
       <c r="F32" s="3">
-        <v>-15600</v>
+        <v>1800</v>
       </c>
       <c r="G32" s="3">
-        <v>6600</v>
+        <v>15600</v>
       </c>
       <c r="H32" s="3">
-        <v>-17900</v>
+        <v>-7800</v>
       </c>
       <c r="I32" s="3">
-        <v>-2100</v>
+        <v>17900</v>
       </c>
       <c r="J32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>18700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-28500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>11500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>600</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E33" s="3">
         <v>32400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>29000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>27000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>12800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>45500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>20200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E35" s="3">
         <v>32400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>29000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>27000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>12800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>45500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>20200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,64 +2397,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>534200</v>
+      </c>
+      <c r="E41" s="3">
         <v>575700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>587200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>617000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>590600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>581100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>544500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>543300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>507900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>492000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>465700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>465900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>449000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>498700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5600</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2424,53 +2513,56 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>68700</v>
+        <v>5596400</v>
       </c>
       <c r="E43" s="3">
-        <v>67800</v>
+        <v>6111200</v>
       </c>
       <c r="F43" s="3">
-        <v>66300</v>
+        <v>5936600</v>
       </c>
       <c r="G43" s="3">
-        <v>65000</v>
+        <v>6411400</v>
       </c>
       <c r="H43" s="3">
-        <v>59000</v>
+        <v>5386300</v>
       </c>
       <c r="I43" s="3">
-        <v>61300</v>
+        <v>5547500</v>
       </c>
       <c r="J43" s="3">
+        <v>5486500</v>
+      </c>
+      <c r="K43" s="3">
         <v>61200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>62500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>60500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>63800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>67500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>59800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>61500</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2480,31 +2572,34 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2536,52 +2631,55 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6088500</v>
+        <v>91700</v>
       </c>
       <c r="E45" s="3">
-        <v>5961200</v>
+        <v>12600</v>
       </c>
       <c r="F45" s="3">
-        <v>6425400</v>
+        <v>60800</v>
       </c>
       <c r="G45" s="3">
-        <v>5405700</v>
+        <v>56700</v>
       </c>
       <c r="H45" s="3">
-        <v>5568900</v>
+        <v>62900</v>
       </c>
       <c r="I45" s="3">
-        <v>5512900</v>
+        <v>55000</v>
       </c>
       <c r="J45" s="3">
+        <v>57200</v>
+      </c>
+      <c r="K45" s="3">
         <v>5866600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5069700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5167400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4656000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4429300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3737700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3655800</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>400</v>
       </c>
       <c r="R45" s="3">
         <v>400</v>
@@ -2590,66 +2688,72 @@
         <v>400</v>
       </c>
       <c r="T45" s="3">
+        <v>400</v>
+      </c>
+      <c r="U45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6249300</v>
+      </c>
+      <c r="E46" s="3">
         <v>6732900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6616100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7108700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6061300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6208900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6118800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6471100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5640200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5719900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5185500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4962700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4246500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4215900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2659,41 +2763,41 @@
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>6400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6600</v>
-      </c>
-      <c r="M47" s="3">
-        <v>7000</v>
       </c>
       <c r="N47" s="3">
         <v>7000</v>
       </c>
       <c r="O47" s="3">
+        <v>7000</v>
+      </c>
+      <c r="P47" s="3">
         <v>6900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6800</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>754800</v>
       </c>
       <c r="R47" s="3">
         <v>754800</v>
@@ -2701,56 +2805,59 @@
       <c r="S47" s="3">
         <v>754800</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>754800</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E48" s="3">
         <v>37600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>37500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>40400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>26100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>26300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>29700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>32000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>30800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>27100</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2760,53 +2867,56 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>176000</v>
+      </c>
+      <c r="E49" s="3">
         <v>108500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>102500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>96200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>90800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>77800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>70000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>65300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>58600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>59300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>60800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>58700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>56900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>57300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2816,8 +2926,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,53 +3044,56 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>41300</v>
+        <v>35300</v>
       </c>
       <c r="E52" s="3">
-        <v>39300</v>
+        <v>22200</v>
       </c>
       <c r="F52" s="3">
-        <v>37900</v>
+        <v>22700</v>
       </c>
       <c r="G52" s="3">
-        <v>39600</v>
+        <v>22600</v>
       </c>
       <c r="H52" s="3">
-        <v>30800</v>
+        <v>23400</v>
       </c>
       <c r="I52" s="3">
-        <v>19400</v>
+        <v>16800</v>
       </c>
       <c r="J52" s="3">
+        <v>17100</v>
+      </c>
+      <c r="K52" s="3">
         <v>22100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>24000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>23900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>26400</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2984,8 +3103,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7051200</v>
+      </c>
+      <c r="E54" s="3">
         <v>6920300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6795500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7283100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6217800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6343900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6237700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6594700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5759500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5842300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5307900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5078800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4360200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4333500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>759200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>760300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>760700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,90 +3269,94 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E57" s="3">
         <v>39000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>35300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>33900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>35600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>31800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>41600</v>
-      </c>
-      <c r="K57" s="3">
-        <v>26700</v>
       </c>
       <c r="L57" s="3">
         <v>26700</v>
       </c>
       <c r="M57" s="3">
+        <v>26700</v>
+      </c>
+      <c r="N57" s="3">
         <v>17400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>16900</v>
       </c>
       <c r="P57" s="3">
         <v>16900</v>
       </c>
       <c r="Q57" s="3">
+        <v>16900</v>
+      </c>
+      <c r="R57" s="3">
         <v>2100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>15000</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
+        <v>20000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>21900</v>
+      </c>
+      <c r="F58" s="3">
+        <v>6400</v>
+      </c>
+      <c r="G58" s="3">
+        <v>7200</v>
+      </c>
+      <c r="H58" s="3">
+        <v>7700</v>
+      </c>
+      <c r="I58" s="3">
+        <v>8200</v>
+      </c>
+      <c r="J58" s="3">
+        <v>9500</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3246,165 +3379,174 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6137500</v>
+        <v>6093800</v>
       </c>
       <c r="E59" s="3">
-        <v>6024900</v>
+        <v>6042400</v>
       </c>
       <c r="F59" s="3">
-        <v>6508000</v>
+        <v>5938700</v>
       </c>
       <c r="G59" s="3">
-        <v>5475200</v>
+        <v>6397000</v>
       </c>
       <c r="H59" s="3">
-        <v>5629300</v>
+        <v>5378100</v>
       </c>
       <c r="I59" s="3">
-        <v>5554300</v>
+        <v>5544200</v>
       </c>
       <c r="J59" s="3">
+        <v>5476100</v>
+      </c>
+      <c r="K59" s="3">
         <v>5935900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5126600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5214100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4699000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4480600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3784100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3755400</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6262600</v>
+      </c>
+      <c r="E60" s="3">
         <v>6191500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6060100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6542000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5510800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5658400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5586100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5977500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5153400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5240900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4716300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4497800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3801000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3772300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>100</v>
       </c>
-      <c r="S60" s="3">
-        <v>0</v>
-      </c>
       <c r="T60" s="3">
+        <v>0</v>
+      </c>
+      <c r="U60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>16500</v>
       </c>
       <c r="E61" s="3">
-        <v>14400</v>
+        <v>16900</v>
       </c>
       <c r="F61" s="3">
-        <v>18400</v>
+        <v>31000</v>
       </c>
       <c r="G61" s="3">
-        <v>15800</v>
+        <v>36200</v>
       </c>
       <c r="H61" s="3">
-        <v>15600</v>
+        <v>19800</v>
       </c>
       <c r="I61" s="3">
-        <v>17100</v>
+        <v>19500</v>
       </c>
       <c r="J61" s="3">
+        <v>22400</v>
+      </c>
+      <c r="K61" s="3">
         <v>16100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3420,64 +3562,70 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>59500</v>
+        <v>42700</v>
       </c>
       <c r="E62" s="3">
-        <v>59400</v>
+        <v>42500</v>
       </c>
       <c r="F62" s="3">
-        <v>58500</v>
+        <v>42800</v>
       </c>
       <c r="G62" s="3">
-        <v>53200</v>
+        <v>40600</v>
       </c>
       <c r="H62" s="3">
-        <v>43800</v>
+        <v>49200</v>
       </c>
       <c r="I62" s="3">
+        <v>40000</v>
+      </c>
+      <c r="J62" s="3">
+        <v>52400</v>
+      </c>
+      <c r="K62" s="3">
+        <v>55700</v>
+      </c>
+      <c r="L62" s="3">
         <v>57700</v>
       </c>
-      <c r="J62" s="3">
-        <v>55700</v>
-      </c>
-      <c r="K62" s="3">
-        <v>57700</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>43700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>55200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>80200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>67300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>79400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>85400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>79500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>30300</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6323300</v>
+      </c>
+      <c r="E66" s="3">
         <v>6250900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6133900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6618800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5579800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5717900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5660900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6049400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5226800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5299400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4785900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4591700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3868300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3851700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>87500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>79600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>30300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3890,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>87800</v>
+      </c>
+      <c r="E72" s="3">
         <v>46200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-15200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-42200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-55000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-100600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-108500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-98400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-71900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-76300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-94100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-75200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-76000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-18200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-9200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-100</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>727900</v>
+      </c>
+      <c r="E76" s="3">
         <v>669400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>661500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>664300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>638000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>625900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>576800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>545300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>532600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>542900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>522000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>487100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>491900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>481800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>671600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>680700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>730400</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E81" s="3">
         <v>32400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>29000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>27000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>12800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>45500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>20200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,64 +4618,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>10700</v>
+        <v>2000</v>
       </c>
       <c r="E83" s="3">
-        <v>9400</v>
+        <v>1900</v>
       </c>
       <c r="F83" s="3">
-        <v>8800</v>
+        <v>2100</v>
       </c>
       <c r="G83" s="3">
-        <v>7100</v>
+        <v>2100</v>
       </c>
       <c r="H83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K83" s="3">
+        <v>5300</v>
+      </c>
+      <c r="L83" s="3">
         <v>5900</v>
       </c>
-      <c r="I83" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>5300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>5900</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>4500</v>
       </c>
       <c r="N83" s="3">
         <v>4500</v>
       </c>
       <c r="O83" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="P83" s="3">
         <v>4400</v>
       </c>
       <c r="Q83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="R83" s="3">
         <v>4700</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E89" s="3">
         <v>41400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>39500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>58200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>41400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>56000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>39600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>15500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>26500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>17800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,64 +5054,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-14500</v>
+        <v>-1600</v>
       </c>
       <c r="E91" s="3">
-        <v>-15700</v>
+        <v>-1200</v>
       </c>
       <c r="F91" s="3">
-        <v>-18100</v>
+        <v>-1600</v>
       </c>
       <c r="G91" s="3">
-        <v>-14300</v>
+        <v>-4100</v>
       </c>
       <c r="H91" s="3">
-        <v>-6000</v>
+        <v>-5500</v>
       </c>
       <c r="I91" s="3">
-        <v>-9400</v>
+        <v>-700</v>
       </c>
       <c r="J91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-11500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1148800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-551200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-114100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>15700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-57000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>19700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>20600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-62500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>28000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>14700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>300</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,31 +5313,32 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5137,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,172 +5547,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E100" s="3">
         <v>77600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-521100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1004700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-177300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>49000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-364500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>805600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-96100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>518200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>233600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>709300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>34200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>650200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2400</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>760800</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-800</v>
+        <v>-1400</v>
       </c>
       <c r="E101" s="3">
-        <v>-1500</v>
+        <v>200</v>
       </c>
       <c r="F101" s="3">
-        <v>5100</v>
+        <v>500</v>
       </c>
       <c r="G101" s="3">
-        <v>-1400</v>
+        <v>700</v>
       </c>
       <c r="H101" s="3">
-        <v>200</v>
+        <v>-900</v>
       </c>
       <c r="I101" s="3">
-        <v>500</v>
+        <v>-2400</v>
       </c>
       <c r="J101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K101" s="3">
         <v>700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-900</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1089700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-432900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-597300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1071500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-121500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>98800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-417100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>865500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-60900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>479800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>263900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>733400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>23000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>669800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
   <si>
     <t>PAYO</t>
   </si>
@@ -656,185 +656,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>261700</v>
+      </c>
+      <c r="E8" s="3">
         <v>248300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>239500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>228200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>224300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>208000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>206700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>192000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>183600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>158900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>148200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>137000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>139200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>122700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>110900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>100600</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E9" s="3">
         <v>38100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>37000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>34000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>36300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>30400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>28500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>27100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -865,35 +871,38 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>218600</v>
+      </c>
+      <c r="E10" s="3">
         <v>210200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>202600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>194200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>188000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>177600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>178200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>164900</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -924,8 +933,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,67 +959,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E12" s="3">
         <v>34600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>27600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>32100</v>
       </c>
-      <c r="G12" s="3">
-        <v>35000</v>
-      </c>
       <c r="H12" s="3">
+        <v>9500</v>
+      </c>
+      <c r="I12" s="3">
         <v>27000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>28000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>29300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>32900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>29600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>26600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>25900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>25500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>20100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>18500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>16700</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,126 +1081,135 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E14" s="3">
         <v>19100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>8000</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>600</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E15" s="3">
         <v>12100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>10700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5700</v>
-      </c>
-      <c r="K15" s="3">
-        <v>5300</v>
       </c>
       <c r="L15" s="3">
         <v>5300</v>
       </c>
       <c r="M15" s="3">
+        <v>5300</v>
+      </c>
+      <c r="N15" s="3">
         <v>5200</v>
-      </c>
-      <c r="N15" s="3">
-        <v>4500</v>
       </c>
       <c r="O15" s="3">
         <v>4500</v>
       </c>
       <c r="P15" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="Q15" s="3">
         <v>4400</v>
       </c>
       <c r="R15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="S15" s="3">
         <v>4600</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1228,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>227300</v>
+      </c>
+      <c r="E17" s="3">
         <v>208800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>193200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>189800</v>
       </c>
-      <c r="G17" s="3">
-        <v>198600</v>
-      </c>
       <c r="H17" s="3">
+        <v>190700</v>
+      </c>
+      <c r="I17" s="3">
         <v>178500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>173300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>176700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>192100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>164000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>150400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>143300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>143400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>129200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>129300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>101800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>100</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E18" s="3">
         <v>39500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>46300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>38400</v>
       </c>
-      <c r="G18" s="3">
-        <v>25700</v>
-      </c>
       <c r="H18" s="3">
+        <v>33700</v>
+      </c>
+      <c r="I18" s="3">
         <v>29500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>33400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>15300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-18400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1200</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,126 +1376,133 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1800</v>
       </c>
-      <c r="G20" s="3">
-        <v>-15600</v>
-      </c>
       <c r="H20" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="I20" s="3">
         <v>7800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-17900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-18700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>28500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-11500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>9200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-600</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E21" s="3">
         <v>51600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>59000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>49500</v>
       </c>
-      <c r="G21" s="3">
-        <v>50000</v>
-      </c>
       <c r="H21" s="3">
+        <v>65800</v>
+      </c>
+      <c r="I21" s="3">
         <v>28800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>57200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>20800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>11000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>26600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-11200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1488,8 +1527,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1521,126 +1560,135 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E23" s="3">
         <v>22100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>48300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>42900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>41300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>22800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>51300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>17100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-23800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>22200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-19500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>15900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>10000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1700</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E26" s="3">
         <v>41600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>32400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>29000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>27000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>12800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>45500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-26500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>20200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-12400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E27" s="3">
         <v>41600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>32400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>29000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>27000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>12800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>45500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-26500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>20200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-12400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,126 +2118,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1800</v>
       </c>
-      <c r="G32" s="3">
-        <v>15600</v>
-      </c>
       <c r="H32" s="3">
+        <v>23400</v>
+      </c>
+      <c r="I32" s="3">
         <v>-7800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>17900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>18700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-28500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>11500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-9200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>600</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E33" s="3">
         <v>41600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>32400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>29000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>27000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>12800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>45500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-26500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>20200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-12400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E35" s="3">
         <v>41600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>32400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>29000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>27000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>12800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>45500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-26500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>20200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-12400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,67 +2483,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>497500</v>
+      </c>
+      <c r="E41" s="3">
         <v>534200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>575700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>587200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>617000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>590600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>581100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>544500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>543300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>507900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>492000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>465700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>465900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>449000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>498700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5600</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,56 +2605,59 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6475700</v>
+      </c>
+      <c r="E43" s="3">
         <v>5596400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6111200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5936600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6411400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5386300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5547500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5486500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>61200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>62500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>60500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>63800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>67500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>59800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>61500</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2575,8 +2667,11 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2601,8 +2696,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2634,55 +2729,58 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>98400</v>
+      </c>
+      <c r="E45" s="3">
         <v>91700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>60800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>56700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>62900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>55000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>57200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5866600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5069700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5167400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4656000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4429300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3737700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3655800</v>
-      </c>
-      <c r="R45" s="3">
-        <v>400</v>
       </c>
       <c r="S45" s="3">
         <v>400</v>
@@ -2691,69 +2789,75 @@
         <v>400</v>
       </c>
       <c r="U45" s="3">
+        <v>400</v>
+      </c>
+      <c r="V45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7099600</v>
+      </c>
+      <c r="E46" s="3">
         <v>6249300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6732900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6616100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7108700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6061300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6208900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6118800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6471100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5640200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5719900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5185500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4962700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4246500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4215900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2778,29 +2882,29 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>6400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6600</v>
-      </c>
-      <c r="N47" s="3">
-        <v>7000</v>
       </c>
       <c r="O47" s="3">
         <v>7000</v>
       </c>
       <c r="P47" s="3">
+        <v>7000</v>
+      </c>
+      <c r="Q47" s="3">
         <v>6900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6800</v>
-      </c>
-      <c r="R47" s="3">
-        <v>754800</v>
       </c>
       <c r="S47" s="3">
         <v>754800</v>
@@ -2808,59 +2912,62 @@
       <c r="T47" s="3">
         <v>754800</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>754800</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E48" s="3">
         <v>36100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>37600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>37500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>40400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>26100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>26300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>29600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>29700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>30800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>27100</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2870,56 +2977,59 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>180200</v>
+      </c>
+      <c r="E49" s="3">
         <v>176000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>108500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>102500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>96200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>90800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>77800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>70000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>65300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>58600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>59300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>60800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>58700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>56900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>57300</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2929,8 +3039,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,56 +3163,59 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E52" s="3">
         <v>35300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22700</v>
       </c>
-      <c r="G52" s="3">
-        <v>22600</v>
-      </c>
       <c r="H52" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I52" s="3">
         <v>23400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>17100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>22400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>24000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>23600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>25300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>23900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>26400</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3106,8 +3225,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3287,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7930400</v>
+      </c>
+      <c r="E54" s="3">
         <v>7051200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6920300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6795500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7283100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6217800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6343900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6237700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6594700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5759500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5842300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5307900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5078800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4360200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4333500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>759200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>760300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>760700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,96 +3399,100 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E57" s="3">
         <v>45100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>39000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>35300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>33900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>35600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>31800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>41600</v>
-      </c>
-      <c r="L57" s="3">
-        <v>26700</v>
       </c>
       <c r="M57" s="3">
         <v>26700</v>
       </c>
       <c r="N57" s="3">
+        <v>26700</v>
+      </c>
+      <c r="O57" s="3">
         <v>17400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17200</v>
-      </c>
-      <c r="P57" s="3">
-        <v>16900</v>
       </c>
       <c r="Q57" s="3">
         <v>16900</v>
       </c>
       <c r="R57" s="3">
+        <v>16900</v>
+      </c>
+      <c r="S57" s="3">
         <v>2100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E58" s="3">
         <v>20000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>21900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9500</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3382,174 +3515,183 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6973800</v>
+      </c>
+      <c r="E59" s="3">
         <v>6093800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6042400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5938700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6397000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5378100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5544200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5476100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5935900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5126600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5214100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4699000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4480600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3784100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3755400</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7131100</v>
+      </c>
+      <c r="E60" s="3">
         <v>6262600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6191500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6060100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6542000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5510800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5658400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5586100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5977500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5153400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5240900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4716300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4497800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3801000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3772300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>100</v>
       </c>
-      <c r="T60" s="3">
-        <v>0</v>
-      </c>
       <c r="U60" s="3">
+        <v>0</v>
+      </c>
+      <c r="V60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E61" s="3">
         <v>16500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>31000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>36200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>19500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>22400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>16100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13700</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3565,67 +3707,73 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E62" s="3">
         <v>42700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>42500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>42800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>40600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>49200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>52400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>55700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>57700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>43700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>55200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>80200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>67300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>79400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>85400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>79500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>30300</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3955,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7205600</v>
+      </c>
+      <c r="E66" s="3">
         <v>6323300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6250900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6133900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6618800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5579800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5717900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5660900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6049400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5226800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5299400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4785900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4591700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3868300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3851700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>87500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>79600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>30300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,67 +4289,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E72" s="3">
         <v>87800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>46200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-15200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-42200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-55000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-100600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-108500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-98400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-71900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-76300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-94100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-75200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-76000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-18200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-9200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-100</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4537,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>724800</v>
+      </c>
+      <c r="E76" s="3">
         <v>727900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>669400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>661500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>664300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>638000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>625900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>576800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>545300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>532600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>542900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>522000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>487100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>491900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>481800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>671600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>680700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>730400</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E81" s="3">
         <v>41600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>32400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>29000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>27000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>12800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>45500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-26500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>20200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-12400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,19 +4816,20 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E83" s="3">
         <v>2000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1900</v>
-      </c>
-      <c r="F83" s="3">
-        <v>2100</v>
       </c>
       <c r="G83" s="3">
         <v>2100</v>
@@ -4640,46 +4838,49 @@
         <v>2100</v>
       </c>
       <c r="I83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J83" s="3">
         <v>2200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>4500</v>
       </c>
       <c r="O83" s="3">
         <v>4500</v>
       </c>
       <c r="P83" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="Q83" s="3">
         <v>4400</v>
       </c>
       <c r="R83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="S83" s="3">
         <v>4700</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E89" s="3">
         <v>50100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>41400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>39500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>58200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>41400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>56000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>39600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>15500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>26500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>17800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-400</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,67 +5274,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-800</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,67 +5458,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-147200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1148800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-551200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-114100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>15700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-57000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>19700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>20600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-62500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>28000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>14700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>300</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5340,8 +5573,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5373,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,181 +5792,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>864700</v>
+      </c>
+      <c r="E100" s="3">
         <v>6500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>77600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-521100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1004700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-177300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>49000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-364500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>805600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-96100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>518200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>233600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>709300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>34200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>650200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2400</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>760800</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-900</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>759700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1089700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-432900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-597300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1071500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-121500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>98800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-417100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>865500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-60900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>479800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>263900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>733400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>23000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>669800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>PAYO</t>
   </si>
@@ -656,194 +656,201 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>246600</v>
+      </c>
+      <c r="E8" s="3">
         <v>261700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>248300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>239500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>228200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>224300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>208000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>206700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>192000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>183600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>158900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>148200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>137000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>139200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>122700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>110900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>100600</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E9" s="3">
         <v>43100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>38100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>37000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>34000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>36300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>28500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>27100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -874,38 +881,41 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>207300</v>
+      </c>
+      <c r="E10" s="3">
         <v>218600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>210200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>202600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>194200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>188000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>177600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>178200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>164900</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -936,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,70 +973,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E12" s="3">
         <v>4600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>34600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>32100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>27000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>28000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>32900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>29600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>26600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>25900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>25500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>20100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>18500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>16700</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,132 +1101,141 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>5200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>19100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>8000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>600</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E15" s="3">
         <v>13200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5700</v>
-      </c>
-      <c r="L15" s="3">
-        <v>5300</v>
       </c>
       <c r="M15" s="3">
         <v>5300</v>
       </c>
       <c r="N15" s="3">
+        <v>5300</v>
+      </c>
+      <c r="O15" s="3">
         <v>5200</v>
-      </c>
-      <c r="O15" s="3">
-        <v>4500</v>
       </c>
       <c r="P15" s="3">
         <v>4500</v>
       </c>
       <c r="Q15" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="R15" s="3">
         <v>4400</v>
       </c>
       <c r="S15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="T15" s="3">
         <v>4600</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>217300</v>
+      </c>
+      <c r="E17" s="3">
         <v>227300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>208800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>193200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>189800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>190700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>178500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>173300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>176700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>192100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>164000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>150400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>143300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>143400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>129200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>129300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>101800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>100</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E18" s="3">
         <v>34400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>39500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>46300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>38400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>33700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>29500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>33400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>15300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-18400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,137 +1410,144 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2400</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
         <v>-2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-23400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-17900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-18700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>28500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-11500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>9200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-600</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E21" s="3">
         <v>50000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>51600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>59000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>49500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>65800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>28800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>57200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>20800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-17900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>11000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>26600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>1600</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>3</v>
@@ -1530,8 +1570,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1563,132 +1603,141 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E23" s="3">
         <v>26200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>48300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>42900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>41300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>22800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>51300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>17100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-23800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>22200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E24" s="3">
         <v>8000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-19500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>15900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1700</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E26" s="3">
         <v>18200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>41600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>32400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>29000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>27000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>12800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>45500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>20200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-12400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E27" s="3">
         <v>18200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>41600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>32400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>29000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>27000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>45500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-26500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>20200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-12400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>2400</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
         <v>2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>23400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>17900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>18700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-28500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>11500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-9200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>600</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E33" s="3">
         <v>18200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>41600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>32400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>29000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>27000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>45500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-26500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>20200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-12400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E35" s="3">
         <v>18200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>41600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>32400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>29000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>27000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>45500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-26500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>20200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-12400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,70 +2570,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>524200</v>
+      </c>
+      <c r="E41" s="3">
         <v>497500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>534200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>575700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>587200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>617000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>590600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>581100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>544500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>543300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>507900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>492000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>465700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>465900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>449000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>498700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5600</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2608,59 +2698,62 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6079300</v>
+      </c>
+      <c r="E43" s="3">
         <v>6475700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5596400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6111200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5936600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6411400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5386300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5547500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5486500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>61200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>62500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>60500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>63800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>67500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>59800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>61500</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2670,8 +2763,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2699,8 +2795,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2732,58 +2828,61 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>64700</v>
+      </c>
+      <c r="E45" s="3">
         <v>98400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>91700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>60800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>56700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>62900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>55000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>57200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5866600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5069700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5167400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4656000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4429300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3737700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3655800</v>
-      </c>
-      <c r="S45" s="3">
-        <v>400</v>
       </c>
       <c r="T45" s="3">
         <v>400</v>
@@ -2792,72 +2891,78 @@
         <v>400</v>
       </c>
       <c r="V45" s="3">
+        <v>400</v>
+      </c>
+      <c r="W45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6712800</v>
+      </c>
+      <c r="E46" s="3">
         <v>7099600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6249300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6732900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6616100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7108700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6061300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6208900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6118800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6471100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5640200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5719900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5185500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4962700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4246500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4215900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2885,29 +2990,29 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>6400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6600</v>
-      </c>
-      <c r="O47" s="3">
-        <v>7000</v>
       </c>
       <c r="P47" s="3">
         <v>7000</v>
       </c>
       <c r="Q47" s="3">
+        <v>7000</v>
+      </c>
+      <c r="R47" s="3">
         <v>6900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6800</v>
-      </c>
-      <c r="S47" s="3">
-        <v>754800</v>
       </c>
       <c r="T47" s="3">
         <v>754800</v>
@@ -2915,62 +3020,65 @@
       <c r="U47" s="3">
         <v>754800</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>754800</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E48" s="3">
         <v>35500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>36100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>37600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>37500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>40400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>26100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>26300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>29600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>29700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>30800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>26000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>27100</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2980,59 +3088,62 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>182500</v>
+      </c>
+      <c r="E49" s="3">
         <v>180200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>176000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>108500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>102500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>96200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>90800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>77800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>70000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>65300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>58600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>59300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>60800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>58700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>56900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>57300</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,59 +3283,62 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E52" s="3">
         <v>38200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>35300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>22700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>23400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>22100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>22400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>24000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>23600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>25300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>23900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>26400</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7550200</v>
+      </c>
+      <c r="E54" s="3">
         <v>7930400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7051200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6920300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6795500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7283100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6217800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6343900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6237700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6594700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5759500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5842300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5307900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5078800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4360200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4333500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>759200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>760300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>760700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,102 +3530,106 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E57" s="3">
         <v>37300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>45100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>39000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>35300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>33900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>35600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>31800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>41600</v>
-      </c>
-      <c r="M57" s="3">
-        <v>26700</v>
       </c>
       <c r="N57" s="3">
         <v>26700</v>
       </c>
       <c r="O57" s="3">
+        <v>26700</v>
+      </c>
+      <c r="P57" s="3">
         <v>17400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17200</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>16900</v>
       </c>
       <c r="R57" s="3">
         <v>16900</v>
       </c>
       <c r="S57" s="3">
+        <v>16900</v>
+      </c>
+      <c r="T57" s="3">
         <v>2100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E58" s="3">
         <v>5700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>20000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>21900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9500</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3518,183 +3652,192 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6600100</v>
+      </c>
+      <c r="E59" s="3">
         <v>6973800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6093800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6042400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5938700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6397000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5378100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5544200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5476100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5935900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5126600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5214100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4699000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4480600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3784100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3755400</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6731000</v>
+      </c>
+      <c r="E60" s="3">
         <v>7131100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6262600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6191500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6060100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6542000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5510800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5658400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5586100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5977500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5153400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5240900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4716300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4497800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3801000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3772300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>100</v>
       </c>
-      <c r="U60" s="3">
-        <v>0</v>
-      </c>
       <c r="V60" s="3">
+        <v>0</v>
+      </c>
+      <c r="W60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E61" s="3">
         <v>15600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>31000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>36200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>19800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>19500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>16100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>15700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13700</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3710,70 +3853,76 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E62" s="3">
         <v>57400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>42700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>42500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>42800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>40600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>49200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>40000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>52400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>55700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>57700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>43700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>55200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>80200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>67300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>79400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>85400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>79500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>30300</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6799400</v>
+      </c>
+      <c r="E66" s="3">
         <v>7205600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6323300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6250900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6133900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6618800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5579800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5717900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5660900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6049400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5226800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5299400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4785900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4591700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3868300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3851700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>87500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>79600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>30300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>126500</v>
+      </c>
+      <c r="E72" s="3">
         <v>106000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>87800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>46200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-15200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-42200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-55000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-100600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-108500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-98400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-71900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-76300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-94100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-75200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-76000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-18200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-9200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-100</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>750700</v>
+      </c>
+      <c r="E76" s="3">
         <v>724800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>727900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>669400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>661500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>664300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>638000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>625900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>576800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>545300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>532600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>542900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>522000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>487100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>491900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>481800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>671600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>680700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>730400</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E81" s="3">
         <v>18200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>41600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>32400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>29000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>27000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>45500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-26500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>20200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-12400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,8 +5015,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4826,13 +5025,13 @@
         <v>2100</v>
       </c>
       <c r="E83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F83" s="3">
         <v>2000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1900</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2100</v>
       </c>
       <c r="H83" s="3">
         <v>2100</v>
@@ -4841,46 +5040,49 @@
         <v>2100</v>
       </c>
       <c r="J83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K83" s="3">
         <v>2200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5200</v>
-      </c>
-      <c r="O83" s="3">
-        <v>4500</v>
       </c>
       <c r="P83" s="3">
         <v>4500</v>
       </c>
       <c r="Q83" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="R83" s="3">
         <v>4400</v>
       </c>
       <c r="S83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="T83" s="3">
         <v>4700</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E89" s="3">
         <v>45900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>50100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>41400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>39500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>58200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>41400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>56000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>39600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>15500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>26500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>17800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-400</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,70 +5495,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-800</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-147200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1148800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-551200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-114100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>15700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-57000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>19700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>20600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-62500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>28000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>14700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>300</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5576,8 +5810,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,190 +6038,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-402400</v>
+      </c>
+      <c r="E100" s="3">
         <v>864700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>77600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-521100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1004700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-177300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>49000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-364500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>805600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-96100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>518200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>233600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>709300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>34200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>650200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>760800</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E101" s="3">
         <v>5100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>-900</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-394800</v>
+      </c>
+      <c r="E102" s="3">
         <v>759700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1089700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-432900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-597300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1071500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-121500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>98800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-417100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>865500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-60900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>479800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>263900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>733400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>23000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>669800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>PAYO</t>
   </si>
@@ -656,204 +656,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>260600</v>
+      </c>
+      <c r="E8" s="3">
         <v>246600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>261700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>248300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>239500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>228200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>224300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>208000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>206700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>192000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>183600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>158900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>148200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>137000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>139200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>122700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>110900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>100600</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E9" s="3">
         <v>39300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>43100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>38100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>37000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>34000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>36300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>30400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>28500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>27100</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -884,41 +891,44 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E10" s="3">
         <v>207300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>218600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>210200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>202600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>194200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>188000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>177600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>178200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>164900</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -949,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>37400</v>
+      </c>
+      <c r="E12" s="3">
         <v>37300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>34600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>27600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>32100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>9500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>27000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>28000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>29300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>32900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>26600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>25900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>25500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>20100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>18500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>16700</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,138 +1121,147 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>5200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>19100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>8000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
         <v>100</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E15" s="3">
         <v>14400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>12100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>10700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5700</v>
-      </c>
-      <c r="M15" s="3">
-        <v>5300</v>
       </c>
       <c r="N15" s="3">
         <v>5300</v>
       </c>
       <c r="O15" s="3">
+        <v>5300</v>
+      </c>
+      <c r="P15" s="3">
         <v>5200</v>
-      </c>
-      <c r="P15" s="3">
-        <v>4500</v>
       </c>
       <c r="Q15" s="3">
         <v>4500</v>
       </c>
       <c r="R15" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="S15" s="3">
         <v>4400</v>
       </c>
       <c r="T15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="U15" s="3">
         <v>4600</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>230500</v>
+      </c>
+      <c r="E17" s="3">
         <v>217300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>227300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>208800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>193200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>189800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>190700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>178500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>173300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>176700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>192100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>164000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>150400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>143300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>143400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>129200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>129300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>101800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>100</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E18" s="3">
         <v>29300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>34400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>39500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>46300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>38400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>33700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>29500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>33400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>15300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-18400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1200</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,147 +1444,154 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2400</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-2000</v>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-23400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>7800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-17900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-18700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>28500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-11500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>8000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>9200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-600</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E21" s="3">
         <v>43700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>50000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>51600</v>
       </c>
-      <c r="G21" s="3">
-        <v>59000</v>
-      </c>
       <c r="H21" s="3">
+        <v>58000</v>
+      </c>
+      <c r="I21" s="3">
         <v>49500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>65800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>28800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>57200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>20800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-17900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>26600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-11200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
         <v>1600</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1573,8 +1613,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1606,138 +1646,147 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E23" s="3">
         <v>27800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>26200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>48300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>42900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>41300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>22800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>51300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>17100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-23800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>22200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E24" s="3">
         <v>7200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-19500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>15900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>13900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>10000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1700</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E26" s="3">
         <v>20600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>18200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>41600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>32400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>29000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>27000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>12800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>45500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-26500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>20200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-12400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E27" s="3">
         <v>20600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>18200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>41600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>32400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>29000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>27000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>12800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>45500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-26500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>20200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-18900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-12400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>2400</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3">
-        <v>2000</v>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I32" s="3">
         <v>1800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>23400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-7800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>17900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>18700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>11500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-8000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-9200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>600</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E33" s="3">
         <v>20600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>18200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>41600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>32400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>29000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>27000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>12800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>45500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-26500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>20200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-18900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-12400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E35" s="3">
         <v>20600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>18200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>41600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>32400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>29000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>27000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>12800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>45500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-26500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>20200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-18900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-12400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,73 +2657,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>497100</v>
+      </c>
+      <c r="E41" s="3">
         <v>524200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>497500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>534200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>575700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>587200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>617000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>590600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>581100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>544500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>543300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>507900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>492000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>465700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>465900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>449000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>498700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5600</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,62 +2791,65 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6620700</v>
+      </c>
+      <c r="E43" s="3">
         <v>6079300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6475700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5596400</v>
       </c>
-      <c r="G43" s="3">
-        <v>6111200</v>
-      </c>
       <c r="H43" s="3">
+        <v>6056300</v>
+      </c>
+      <c r="I43" s="3">
         <v>5936600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6411400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5386300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5547500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5486500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>61200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>62500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>60500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>63800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>67500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>59800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>61500</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2766,8 +2859,11 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2798,8 +2894,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2831,61 +2927,64 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>55700</v>
+      </c>
+      <c r="E45" s="3">
         <v>64700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>98400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>91700</v>
       </c>
-      <c r="G45" s="3">
-        <v>12600</v>
-      </c>
       <c r="H45" s="3">
+        <v>67500</v>
+      </c>
+      <c r="I45" s="3">
         <v>60800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>56700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>62900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>55000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>57200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5866600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5069700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5167400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4656000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4429300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3737700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3655800</v>
-      </c>
-      <c r="T45" s="3">
-        <v>400</v>
       </c>
       <c r="U45" s="3">
         <v>400</v>
@@ -2894,75 +2993,81 @@
         <v>400</v>
       </c>
       <c r="W45" s="3">
+        <v>400</v>
+      </c>
+      <c r="X45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7212500</v>
+      </c>
+      <c r="E46" s="3">
         <v>6712800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7099600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6249300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6732900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6616100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7108700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6061300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6208900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6118800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6471100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5640200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5719900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5185500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4962700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4246500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4215900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2993,29 +3098,29 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>6400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6600</v>
-      </c>
-      <c r="P47" s="3">
-        <v>7000</v>
       </c>
       <c r="Q47" s="3">
         <v>7000</v>
       </c>
       <c r="R47" s="3">
+        <v>7000</v>
+      </c>
+      <c r="S47" s="3">
         <v>6900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>6800</v>
-      </c>
-      <c r="T47" s="3">
-        <v>754800</v>
       </c>
       <c r="U47" s="3">
         <v>754800</v>
@@ -3023,65 +3128,68 @@
       <c r="V47" s="3">
         <v>754800</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>754800</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>62700</v>
+      </c>
+      <c r="E48" s="3">
         <v>37100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>35500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>36100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>37600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>37500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>40400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>26100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>26300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>29600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>29700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>30800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>26000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>27100</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,62 +3199,65 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>281700</v>
+      </c>
+      <c r="E49" s="3">
         <v>182500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>180200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>176000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>108500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>102500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>96200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>90800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>77800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>70000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>65300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>58600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>59300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>60800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>58700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>56900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>57300</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,62 +3403,65 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E52" s="3">
         <v>51500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>38200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>35300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>22200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>22700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>23400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>22100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>22400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>24000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>23600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>25300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>23900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>26400</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8110400</v>
+      </c>
+      <c r="E54" s="3">
         <v>7550200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7930400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7051200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6920300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6795500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7283100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6217800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6343900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6237700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6594700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5759500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5842300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5307900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5078800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4360200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4333500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>759200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>760300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>760700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,108 +3661,112 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E57" s="3">
         <v>32900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>37300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>45100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>39000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>35300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>33900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>35600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>29200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>31800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>41600</v>
-      </c>
-      <c r="N57" s="3">
-        <v>26700</v>
       </c>
       <c r="O57" s="3">
         <v>26700</v>
       </c>
       <c r="P57" s="3">
+        <v>26700</v>
+      </c>
+      <c r="Q57" s="3">
         <v>17400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17200</v>
-      </c>
-      <c r="R57" s="3">
-        <v>16900</v>
       </c>
       <c r="S57" s="3">
         <v>16900</v>
       </c>
       <c r="T57" s="3">
+        <v>16900</v>
+      </c>
+      <c r="U57" s="3">
         <v>2100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E58" s="3">
         <v>7200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>20000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>21900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9500</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -3655,192 +3789,201 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7058200</v>
+      </c>
+      <c r="E59" s="3">
         <v>6600100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6973800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6093800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6042400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5938700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6397000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5378100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5544200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5476100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5935900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5126600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5214100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4699000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4480600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3784100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3755400</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7208200</v>
+      </c>
+      <c r="E60" s="3">
         <v>6731000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7131100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6262600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6191500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6060100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6542000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5510800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5658400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5586100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5977500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5153400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5240900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4716300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4497800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3801000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3772300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>100</v>
       </c>
-      <c r="V60" s="3">
-        <v>0</v>
-      </c>
       <c r="W60" s="3">
+        <v>0</v>
+      </c>
+      <c r="X60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E61" s="3">
         <v>14700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>31000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>36200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>19800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>22400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>16100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13700</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3856,73 +3999,79 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>66900</v>
+      </c>
+      <c r="E62" s="3">
         <v>52300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>57400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>42700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>42500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>42800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>49200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>40000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>52400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>55700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>57700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>43700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>55200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>80200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>67300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>79400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>85400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>79500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>30300</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7339500</v>
+      </c>
+      <c r="E66" s="3">
         <v>6799400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7205600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6323300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6250900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6133900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6618800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5579800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5717900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5660900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6049400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5226800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5299400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4785900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4591700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3868300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3851700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>87500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>79600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>30300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>146000</v>
+      </c>
+      <c r="E72" s="3">
         <v>126500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>106000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>87800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>46200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>13800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-15200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-42200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-55000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-100600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-108500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-98400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-71900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-76300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-94100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-75200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-76000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-18200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-9200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-100</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>770900</v>
+      </c>
+      <c r="E76" s="3">
         <v>750700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>724800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>727900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>669400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>661500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>664300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>638000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>625900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>576800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>545300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>532600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>542900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>522000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>487100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>491900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>481800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>671600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>680700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>730400</v>
       </c>
-      <c r="W76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E81" s="3">
         <v>20600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>18200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>41600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>32400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>29000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>27000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>12800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>45500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-26500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>20200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-18900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-12400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5028,13 +5227,13 @@
         <v>2100</v>
       </c>
       <c r="F83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G83" s="3">
         <v>2000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1900</v>
-      </c>
-      <c r="H83" s="3">
-        <v>2100</v>
       </c>
       <c r="I83" s="3">
         <v>2100</v>
@@ -5043,46 +5242,49 @@
         <v>2100</v>
       </c>
       <c r="K83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L83" s="3">
         <v>2200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5200</v>
-      </c>
-      <c r="P83" s="3">
-        <v>4500</v>
       </c>
       <c r="Q83" s="3">
         <v>4500</v>
       </c>
       <c r="R83" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="S83" s="3">
         <v>4400</v>
       </c>
       <c r="T83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="U83" s="3">
         <v>4700</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E89" s="3">
         <v>53700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>45900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>50100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>41400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>39500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>58200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>41400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>56000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>39600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>15500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>26500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>17800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-400</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-800</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-85500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-48000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-147200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1148800</v>
       </c>
-      <c r="G94" s="3">
-        <v>-551200</v>
-      </c>
       <c r="H94" s="3">
+        <v>-851200</v>
+      </c>
+      <c r="I94" s="3">
         <v>-114100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>15700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-57000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>19700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>20600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-62500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>28000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>14700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>300</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5813,8 +6047,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,199 +6284,211 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>404700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-402400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>864700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>77600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-521100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1004700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-177300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>49000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-364500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>805600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-96100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>518200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>233600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>709300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>34200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>650200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2400</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>760800</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-500</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-900</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>394000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-394800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>759700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1089700</v>
       </c>
-      <c r="G102" s="3">
-        <v>-432900</v>
-      </c>
       <c r="H102" s="3">
+        <v>-732900</v>
+      </c>
+      <c r="I102" s="3">
         <v>-597300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1071500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-121500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>98800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-417100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>865500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-60900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>479800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>263900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>733400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>23000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>669800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
   <si>
     <t>PAYO</t>
   </si>
@@ -656,224 +656,230 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>274700</v>
+      </c>
+      <c r="E8" s="3">
         <v>270900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>260600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>246600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>261700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>248300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>239500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>228200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>224300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>208000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>206700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>192000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>183600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>158900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>148200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>137000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>139200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>122700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>110900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>100600</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E9" s="3">
         <v>42500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>40600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>39300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>43100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>38100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>37000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>34000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>36300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>30400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>28500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>27100</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -904,47 +910,50 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>231900</v>
+      </c>
+      <c r="E10" s="3">
         <v>228400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>220000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>207300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>218600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>210200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>202600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>194200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>188000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>177600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>178200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>164900</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -975,8 +984,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,79 +1014,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E12" s="3">
         <v>39900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>37400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>37300</v>
       </c>
-      <c r="G12" s="3">
-        <v>4600</v>
-      </c>
       <c r="H12" s="3">
+        <v>40400</v>
+      </c>
+      <c r="I12" s="3">
         <v>34600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>27600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>32100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>27000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>28000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>32900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>29600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>26600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>25900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>25500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>20100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>18500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>16700</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,150 +1160,159 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I14" s="3">
+        <v>19300</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>8000</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
+        <v>300</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>600</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>5200</v>
-      </c>
-      <c r="H14" s="3">
-        <v>16100</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>8000</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
-        <v>300</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V14" s="3">
-        <v>100</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E15" s="3">
         <v>16100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>15600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>13200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>10700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5700</v>
-      </c>
-      <c r="O15" s="3">
-        <v>5300</v>
       </c>
       <c r="P15" s="3">
         <v>5300</v>
       </c>
       <c r="Q15" s="3">
+        <v>5300</v>
+      </c>
+      <c r="R15" s="3">
         <v>5200</v>
-      </c>
-      <c r="R15" s="3">
-        <v>4500</v>
       </c>
       <c r="S15" s="3">
         <v>4500</v>
       </c>
       <c r="T15" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="U15" s="3">
         <v>4400</v>
       </c>
       <c r="V15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="W15" s="3">
         <v>4600</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>234400</v>
+        <v>240300</v>
       </c>
       <c r="E17" s="3">
+        <v>233500</v>
+      </c>
+      <c r="F17" s="3">
         <v>230400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>217300</v>
       </c>
-      <c r="G17" s="3">
-        <v>227300</v>
-      </c>
       <c r="H17" s="3">
-        <v>211700</v>
+        <v>230300</v>
       </c>
       <c r="I17" s="3">
+        <v>208600</v>
+      </c>
+      <c r="J17" s="3">
         <v>193200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>189800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>190700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>178500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>173300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>176700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>192100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>164000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>150400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>143300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>143400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>129200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>129300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>101800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>100</v>
       </c>
-      <c r="Y17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>36500</v>
+        <v>34400</v>
       </c>
       <c r="E18" s="3">
+        <v>37300</v>
+      </c>
+      <c r="F18" s="3">
         <v>30200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>29300</v>
       </c>
-      <c r="G18" s="3">
-        <v>34400</v>
-      </c>
       <c r="H18" s="3">
-        <v>36500</v>
+        <v>31500</v>
       </c>
       <c r="I18" s="3">
+        <v>39700</v>
+      </c>
+      <c r="J18" s="3">
         <v>46300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>38400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>33700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>29500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>33400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>15300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-6500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-18400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1200</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,8 +1511,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1493,151 +1526,157 @@
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
+        <v>3000</v>
       </c>
       <c r="I20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J20" s="3">
         <v>-2000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-23400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-17900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-18700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>28500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-11500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>8000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>9200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-600</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>52600</v>
+        <v>52000</v>
       </c>
       <c r="E21" s="3">
+        <v>53500</v>
+      </c>
+      <c r="F21" s="3">
         <v>45700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>43700</v>
       </c>
-      <c r="G21" s="3">
-        <v>50000</v>
-      </c>
       <c r="H21" s="3">
-        <v>48700</v>
+        <v>41700</v>
       </c>
       <c r="I21" s="3">
+        <v>53500</v>
+      </c>
+      <c r="J21" s="3">
         <v>59000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>52300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>65800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>28800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>57200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>20800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-17900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>26600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-11200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2900</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E22" s="3">
         <v>5800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1600</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1659,8 +1698,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1692,150 +1731,159 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E23" s="3">
         <v>30500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>29900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>27800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>26200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>22100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>48300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>42900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>41300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>22800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>51300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>17100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-23800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>22200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-15800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-9100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-100</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E24" s="3">
         <v>16400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-19500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>15900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>13900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>10000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1700</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E26" s="3">
         <v>14100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>19500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>20600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>18200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>41600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>32400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>29000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>27000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>12800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>45500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>20200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-18900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-12400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-100</v>
       </c>
-      <c r="Y26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E27" s="3">
         <v>14100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>19500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>20600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>18200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>41600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>32400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>29000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>27000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>45500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>20200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-18900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-12400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-100</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,8 +2397,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2345,136 +2414,142 @@
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-3000</v>
       </c>
       <c r="I32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J32" s="3">
         <v>2000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>23400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>17900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>18700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-28500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>11500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-8000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-9200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>600</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E33" s="3">
         <v>14100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>19500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>20600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>18200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>41600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>32400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>29000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>27000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>12800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>45500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>20200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-18900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-12400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-100</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E35" s="3">
         <v>14100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>19500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>20600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>18200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>41600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>32400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>29000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>27000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>12800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>45500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>20200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-18900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-12400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-100</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,79 +2830,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>415500</v>
+      </c>
+      <c r="E41" s="3">
         <v>479400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>497100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>524200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>497500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>534200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>575700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>587200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>617000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>590600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>581100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>544500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>543300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>507900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>492000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>465700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>465900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>449000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>498700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5600</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,68 +2976,71 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7598600</v>
+      </c>
+      <c r="E43" s="3">
         <v>6819900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6620700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6079300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6475700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5596400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6056300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5936600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6411400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5386300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5547500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5486500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>61200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>62500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>60500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>63800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>67500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>59800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>61500</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2958,8 +3050,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2996,8 +3091,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3029,67 +3124,70 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E45" s="3">
         <v>66500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>55700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>64700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>98400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>91700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>67500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>60800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>56700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>62900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>55000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>57200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5866600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5069700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5167400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4656000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4429300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3737700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3655800</v>
-      </c>
-      <c r="V45" s="3">
-        <v>400</v>
       </c>
       <c r="W45" s="3">
         <v>400</v>
@@ -3098,81 +3196,87 @@
         <v>400</v>
       </c>
       <c r="Y45" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8110900</v>
+      </c>
+      <c r="E46" s="3">
         <v>7401400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7212500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6712800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7099600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6249300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6732900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6616100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7108700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6061300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6208900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6118800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6471100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5640200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5719900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5185500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4962700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4246500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4215900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3209,29 +3313,29 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>6400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6600</v>
-      </c>
-      <c r="R47" s="3">
-        <v>7000</v>
       </c>
       <c r="S47" s="3">
         <v>7000</v>
       </c>
       <c r="T47" s="3">
+        <v>7000</v>
+      </c>
+      <c r="U47" s="3">
         <v>6900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6800</v>
-      </c>
-      <c r="V47" s="3">
-        <v>754800</v>
       </c>
       <c r="W47" s="3">
         <v>754800</v>
@@ -3239,71 +3343,74 @@
       <c r="X47" s="3">
         <v>754800</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>754800</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E48" s="3">
         <v>69300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>62700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>37100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>35500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>36100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>37600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>37500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>40400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>26100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>26300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>29600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>29700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>32000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>32500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>30800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>25100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>26000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>27100</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3313,68 +3420,71 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>285800</v>
+      </c>
+      <c r="E49" s="3">
         <v>283700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>281700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>182500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>180200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>176000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>108500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>102500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>96200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>90800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>77800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>70000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>65300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>58600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>59300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>60800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>58700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>56900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>57300</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3384,8 +3494,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,68 +3642,71 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E52" s="3">
         <v>51200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>58900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>51500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>38200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>35300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>22700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>23400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>17100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>22100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>22400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>24000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>23600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>25300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>23900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>26400</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3597,8 +3716,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3790,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8956600</v>
+      </c>
+      <c r="E54" s="3">
         <v>8205500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8110400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7550200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7930400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7051200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6920300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6795500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7283100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6217800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6343900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6237700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6594700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5759500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5842300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5307900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5078800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4360200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4333500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>759200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>760300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>760700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,120 +3922,124 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E57" s="3">
         <v>39700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>42400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>37300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>45100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>39000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>35300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>33900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>35600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>29200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>31800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>41600</v>
-      </c>
-      <c r="P57" s="3">
-        <v>26700</v>
       </c>
       <c r="Q57" s="3">
         <v>26700</v>
       </c>
       <c r="R57" s="3">
+        <v>26700</v>
+      </c>
+      <c r="S57" s="3">
         <v>17400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17200</v>
-      </c>
-      <c r="T57" s="3">
-        <v>16900</v>
       </c>
       <c r="U57" s="3">
         <v>16900</v>
       </c>
       <c r="V57" s="3">
+        <v>16900</v>
+      </c>
+      <c r="W57" s="3">
         <v>2100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6600</v>
+        <v>7200</v>
       </c>
       <c r="E58" s="3">
         <v>6600</v>
       </c>
       <c r="F58" s="3">
+        <v>6600</v>
+      </c>
+      <c r="G58" s="3">
         <v>7200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>20000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>21900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9500</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -3929,210 +4062,219 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7916800</v>
+      </c>
+      <c r="E59" s="3">
         <v>7148600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7058200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6600100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6973800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6093800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6042400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5938700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6397000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5378100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5544200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5476100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5935900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5126600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5214100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4699000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4480600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3784100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3755400</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8083700</v>
+      </c>
+      <c r="E60" s="3">
         <v>7308300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7208200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6731000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7131100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6262600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6191500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6060100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6542000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5510800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5658400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5586100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5977500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5153400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5240900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4716300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4497800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3801000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3772300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>100</v>
       </c>
-      <c r="X60" s="3">
-        <v>0</v>
-      </c>
       <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E61" s="3">
         <v>47900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>39300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>31000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>36200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>19800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>19500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>22400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>16100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>15700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13700</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4148,79 +4290,85 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E62" s="3">
         <v>73700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>66900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>52300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>57400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>42700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>42500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>42800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>40600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>49200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>40000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>52400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>55700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>57700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>43700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>55200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>80200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>67300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>79400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>85400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>79500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>30300</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8252200</v>
+      </c>
+      <c r="E66" s="3">
         <v>7455000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7339500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6799400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7205600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6323300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6250900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6133900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6618800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5579800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5717900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5660900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6049400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5226800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5299400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4785900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4591700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3868300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3851700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>87500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>79600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>30300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4984,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>179200</v>
+      </c>
+      <c r="E72" s="3">
         <v>160100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>146000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>126500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>106000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>87800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>46200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-15200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-42200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-55000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-100600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-108500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-98400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-71900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-76300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-94100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-75200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-76000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-18200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-9200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-100</v>
       </c>
-      <c r="Y72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>704400</v>
+      </c>
+      <c r="E76" s="3">
         <v>750500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>770900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>750700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>724800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>727900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>669400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>661500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>664300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>638000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>625900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>576800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>545300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>532600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>542900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>522000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>487100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>491900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>481800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>671600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>680700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>730400</v>
       </c>
-      <c r="Y76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E81" s="3">
         <v>14100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>19500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>20600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>18200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>41600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>32400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>29000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>27000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>12800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>45500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>20200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-18900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-12400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-100</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5611,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5432,13 +5630,13 @@
         <v>2100</v>
       </c>
       <c r="H83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I83" s="3">
         <v>2000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>2100</v>
       </c>
       <c r="K83" s="3">
         <v>2100</v>
@@ -5447,46 +5645,49 @@
         <v>2100</v>
       </c>
       <c r="M83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N83" s="3">
         <v>2200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5200</v>
-      </c>
-      <c r="R83" s="3">
-        <v>4500</v>
       </c>
       <c r="S83" s="3">
         <v>4500</v>
       </c>
       <c r="T83" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="U83" s="3">
         <v>4400</v>
       </c>
       <c r="V83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="W83" s="3">
         <v>4700</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E89" s="3">
         <v>54200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>70700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>53700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>45900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>50100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>41400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>39500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>58200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>41400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>56000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>39600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>15500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>26500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>17800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,79 +6157,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-800</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6377,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-35900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-85500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-48000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-147200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-848800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-851200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-114100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>15700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-57000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>19700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>20600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-62500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>28000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>14700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>300</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
+      <c r="X94" s="3">
+        <v>0</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6287,8 +6520,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6320,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,217 +6775,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>701000</v>
+      </c>
+      <c r="E100" s="3">
         <v>34800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>404700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-402400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>864700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>77600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-521100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1004700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-177300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>49000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-364500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>805600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-96100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>518200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>233600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>709300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>34200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>650200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>760800</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E101" s="3">
         <v>2400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>5100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-500</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-900</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>707100</v>
+      </c>
+      <c r="E102" s="3">
         <v>52200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>394000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-394800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>759700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-789700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-732900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-597300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1071500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-121500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>98800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-417100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>865500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-60900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>479800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>263900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>733400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>23000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>669800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PAYO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
   <si>
     <t>PAYO</t>
   </si>
@@ -656,233 +656,240 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>261600</v>
+      </c>
+      <c r="E8" s="3">
         <v>274700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>270900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>260600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>246600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>261700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>248300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>239500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>228200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>224300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>208000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>206700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>192000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>183600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>158900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>148200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>137000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>139200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>122700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>110900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>100600</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E9" s="3">
         <v>42800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>42500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>40600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>39300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>43100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>38100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>37000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>34000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>36300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>30400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>28500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>27100</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -913,50 +920,53 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>226400</v>
+      </c>
+      <c r="E10" s="3">
         <v>231900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>228400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>220000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>207300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>218600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>210200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>202600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>194200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>188000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>177600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>178200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>164900</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,8 +997,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,82 +1028,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E12" s="3">
         <v>40500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>39900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>37400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>37300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>40400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>34600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>27600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>32100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>27000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>28000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>29300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>32900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>29600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>26600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>25900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>25500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>20100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>18500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>16700</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,156 +1180,165 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>5500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>2300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>19300</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>8000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>600</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
         <v>100</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E15" s="3">
         <v>17600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>16100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>15600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>10700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5700</v>
-      </c>
-      <c r="P15" s="3">
-        <v>5300</v>
       </c>
       <c r="Q15" s="3">
         <v>5300</v>
       </c>
       <c r="R15" s="3">
+        <v>5300</v>
+      </c>
+      <c r="S15" s="3">
         <v>5200</v>
-      </c>
-      <c r="S15" s="3">
-        <v>4500</v>
       </c>
       <c r="T15" s="3">
         <v>4500</v>
       </c>
       <c r="U15" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="V15" s="3">
         <v>4400</v>
       </c>
       <c r="W15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="X15" s="3">
         <v>4600</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>231600</v>
+      </c>
+      <c r="E17" s="3">
         <v>240300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>233500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>230400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>217300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>230300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>208600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>193200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>189800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>190700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>178500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>173300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>176700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>192100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>164000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>150400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>143300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>143400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>129200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>129300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>101800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>100</v>
       </c>
-      <c r="Z17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E18" s="3">
         <v>34400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>37300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>30200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>29300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>31500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>39700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>46300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>38400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>33700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>29500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>33400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>15300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-6500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-18400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1200</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,8 +1545,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1529,157 +1563,163 @@
       <c r="G20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-23400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-17900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-18700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>8000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>28500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-11500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>8000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-600</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E21" s="3">
         <v>52000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>53500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>45700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>43700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>41700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>53500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>59000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>52300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>65800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>28800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>57200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>20800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-17900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>26600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-11200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-4900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2900</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>800</v>
+      </c>
+      <c r="E22" s="3">
         <v>1500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1600</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1701,8 +1741,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1734,156 +1774,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E23" s="3">
         <v>27500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>30500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>29900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>27800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>26200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>22100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>48300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>42900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>41300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>22800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>51300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>17100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-23800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>22200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-15800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-9200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E24" s="3">
         <v>8400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>16400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-19500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>13900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1700</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E26" s="3">
         <v>19000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>14100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>19500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>20600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>18200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>41600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>32400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>29000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>27000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>12800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>45500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-26500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>20200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-18900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-12400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E27" s="3">
         <v>19000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>14100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>19500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>20600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>18200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>41600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>32400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>29000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>27000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>12800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>45500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-26500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>20200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-18900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-12400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-100</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,8 +2467,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2417,139 +2487,145 @@
       <c r="G32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>-3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>23400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>17900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>18700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-8000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-28500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>11500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-8000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>600</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E33" s="3">
         <v>19000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>14100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>19500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>20600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>18200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>41600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>32400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>29000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>27000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>12800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>45500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-26500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>20200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-18900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-12400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-100</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E35" s="3">
         <v>19000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>14100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>19500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>20600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>18200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>41600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>32400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>29000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>27000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>12800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>45500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-26500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>20200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-18900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-12400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-100</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,82 +2917,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>339400</v>
+      </c>
+      <c r="E41" s="3">
         <v>415500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>479400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>497100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>524200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>497500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>534200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>575700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>587200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>617000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>590600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>581100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>544500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>543300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>507900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>492000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>465700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>465900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>449000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>498700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5600</v>
       </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2979,71 +3069,74 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7290400</v>
+      </c>
+      <c r="E43" s="3">
         <v>7598600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6819900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6620700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6079300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6475700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5596400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6056300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5936600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6411400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5386300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5547500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5486500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>61200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>62500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>60500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>63800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>67500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>59800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>61500</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3053,8 +3146,11 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3094,8 +3190,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3127,70 +3223,73 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E45" s="3">
         <v>64600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>66500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>55700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>64700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>98400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>91700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>67500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>60800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>56700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>62900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>55000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>57200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5866600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5069700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5167400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4656000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4429300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3737700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3655800</v>
-      </c>
-      <c r="W45" s="3">
-        <v>400</v>
       </c>
       <c r="X45" s="3">
         <v>400</v>
@@ -3199,84 +3298,90 @@
         <v>400</v>
       </c>
       <c r="Z45" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7723500</v>
+      </c>
+      <c r="E46" s="3">
         <v>8110900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7401400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7212500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6712800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7099600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6249300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6732900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6616100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7108700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6061300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6208900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6118800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6471100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5640200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5719900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5185500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4962700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4246500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4215900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3316,29 +3421,29 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>6400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6600</v>
-      </c>
-      <c r="S47" s="3">
-        <v>7000</v>
       </c>
       <c r="T47" s="3">
         <v>7000</v>
       </c>
       <c r="U47" s="3">
+        <v>7000</v>
+      </c>
+      <c r="V47" s="3">
         <v>6900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>6800</v>
-      </c>
-      <c r="W47" s="3">
-        <v>754800</v>
       </c>
       <c r="X47" s="3">
         <v>754800</v>
@@ -3346,74 +3451,77 @@
       <c r="Y47" s="3">
         <v>754800</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>754800</v>
+      </c>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>103500</v>
+      </c>
+      <c r="E48" s="3">
         <v>94700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>69300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>62700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>37100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>35500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>36100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>37600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>37500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>40400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>26100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>29600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>29700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>32000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>32500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>30800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>25100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>26000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>27100</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3423,71 +3531,74 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>300600</v>
+      </c>
+      <c r="E49" s="3">
         <v>285800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>283700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>281700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>182500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>180200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>176000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>108500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>102500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>96200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>90800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>77800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>70000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>65300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>58600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>59300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>60800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>58700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>56900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>57300</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,71 +3762,74 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E52" s="3">
         <v>47600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>51200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>58900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>51500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>38200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>35300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>22200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>17100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>22100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>22400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>24000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>23600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>25300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>23900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>26400</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3719,8 +3839,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8598000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8956600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8205500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8110400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7550200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7930400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7051200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6920300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6795500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7283100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6217800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6343900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6237700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6594700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5759500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5842300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5307900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5078800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4360200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4333500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>759200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>760300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>760700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,126 +4053,130 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E57" s="3">
         <v>44600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>39700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>42400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>32900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>37300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>45100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>39000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>35300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>33900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>35600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>29200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>31800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>41600</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>26700</v>
       </c>
       <c r="R57" s="3">
         <v>26700</v>
       </c>
       <c r="S57" s="3">
+        <v>26700</v>
+      </c>
+      <c r="T57" s="3">
         <v>17400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>17200</v>
-      </c>
-      <c r="U57" s="3">
-        <v>16900</v>
       </c>
       <c r="V57" s="3">
         <v>16900</v>
       </c>
       <c r="W57" s="3">
+        <v>16900</v>
+      </c>
+      <c r="X57" s="3">
         <v>2100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>100</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E58" s="3">
         <v>7200</v>
-      </c>
-      <c r="E58" s="3">
-        <v>6600</v>
       </c>
       <c r="F58" s="3">
         <v>6600</v>
       </c>
       <c r="G58" s="3">
+        <v>6600</v>
+      </c>
+      <c r="H58" s="3">
         <v>7200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>20000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>21900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9500</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -4065,219 +4199,228 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7617400</v>
+      </c>
+      <c r="E59" s="3">
         <v>7916800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7148600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7058200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6600100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6973800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6093800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6042400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5938700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6397000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5378100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5544200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5476100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5935900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5126600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5214100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4699000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4480600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3784100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3755400</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA59" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7761900</v>
+      </c>
+      <c r="E60" s="3">
         <v>8083700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7308300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7208200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6731000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7131100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6262600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6191500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6060100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6542000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5510800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5658400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5586100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5977500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5153400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5240900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4716300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4497800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3801000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3772300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>100</v>
       </c>
-      <c r="Y60" s="3">
-        <v>0</v>
-      </c>
       <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E61" s="3">
         <v>65100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>47900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>39300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>15600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>31000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>36200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>19800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>19500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>16100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>15700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>13700</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4293,82 +4436,88 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E62" s="3">
         <v>78300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>73700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>66900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>52300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>57400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>42700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>42500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>42800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>40600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>49200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>40000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>52400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>55700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>57700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>43700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>55200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>80200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>67300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>79400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>85400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>79500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>30300</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7938900</v>
+      </c>
+      <c r="E66" s="3">
         <v>8252200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7455000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7339500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6799400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7205600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6323300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6250900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6133900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6618800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5579800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5717900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5660900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6049400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5226800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5299400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4785900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4591700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3868300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3851700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>87500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>79600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>30300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>198700</v>
+      </c>
+      <c r="E72" s="3">
         <v>179200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>160100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>146000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>126500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>106000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>87800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>46200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-15200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-42200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-55000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-100600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-108500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-98400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-71900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-76300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-94100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-75200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-76000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-18200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-100</v>
       </c>
-      <c r="Z72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>659100</v>
+      </c>
+      <c r="E76" s="3">
         <v>704400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>750500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>770900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>750700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>724800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>727900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>669400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>661500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>664300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>638000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>625900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>576800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>545300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>532600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>542900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>522000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>487100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>491900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>481800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>671600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>680700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>730400</v>
       </c>
-      <c r="Z76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E81" s="3">
         <v>19000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>14100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>19500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>20600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>18200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>41600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>32400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>29000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>27000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>12800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>45500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-26500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>20200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-18900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-12400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-100</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5633,13 +5832,13 @@
         <v>2100</v>
       </c>
       <c r="I83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J83" s="3">
         <v>2000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1900</v>
-      </c>
-      <c r="K83" s="3">
-        <v>2100</v>
       </c>
       <c r="L83" s="3">
         <v>2100</v>
@@ -5648,46 +5847,49 @@
         <v>2100</v>
       </c>
       <c r="N83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O83" s="3">
         <v>2200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5200</v>
-      </c>
-      <c r="S83" s="3">
-        <v>4500</v>
       </c>
       <c r="T83" s="3">
         <v>4500</v>
       </c>
       <c r="U83" s="3">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="V83" s="3">
         <v>4400</v>
       </c>
       <c r="W83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="X83" s="3">
         <v>4700</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E89" s="3">
         <v>54900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>54200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>70700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>53700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>45900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>50100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>41400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>39500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>58200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>41400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>56000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>39600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>15500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>26500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-5900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>17800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-400</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,82 +6378,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-800</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-60900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-49000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-35900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-85500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-48000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-147200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-848800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-851200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-114100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>15700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-57000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>19700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>20600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-62500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>28000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>14700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>300</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
+      <c r="Y94" s="3">
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6523,8 +6757,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,226 +7021,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-385700</v>
+      </c>
+      <c r="E100" s="3">
         <v>701000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>34800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>404700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-402400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>864700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>77600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-521100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1004700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-177300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>49000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-364500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>805600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-96100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>518200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>233600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>709300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>34200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>650200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2400</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>760800</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>5100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-500</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-900</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-395500</v>
+      </c>
+      <c r="E102" s="3">
         <v>707100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>52200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>394000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-394800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>759700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-789700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-732900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-597300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1071500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-121500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>98800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-417100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>865500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-60900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>479800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>263900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>733400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>23000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>669800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>
